--- a/German Bundesliga/X_pred.xlsx
+++ b/German Bundesliga/X_pred.xlsx
@@ -1547,16 +1547,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1580,19 +1580,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -1604,67 +1604,67 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -1685,19 +1685,19 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -1706,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
@@ -1715,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>1</v>
@@ -1727,10 +1727,10 @@
         <v>1</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
@@ -1739,136 +1739,136 @@
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.417533432392273</v>
+        <v>2.555720653789004</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.74888558692422</v>
+        <v>4.13075780089153</v>
       </c>
       <c r="BO2" t="n">
-        <v>21.84487369985141</v>
+        <v>35.111441307578</v>
       </c>
       <c r="BP2" t="n">
-        <v>9.49777117384844</v>
+        <v>12.80534918276374</v>
       </c>
       <c r="BQ2" t="n">
-        <v>140.5670133729569</v>
+        <v>124.3358098068351</v>
       </c>
       <c r="BR2" t="n">
-        <v>26.11887072808321</v>
+        <v>20.2407132243685</v>
       </c>
       <c r="BS2" t="n">
-        <v>13.77176820208024</v>
+        <v>15.28380386329866</v>
       </c>
       <c r="BT2" t="n">
-        <v>47.4888558692422</v>
+        <v>46.26448736998513</v>
       </c>
       <c r="BU2" t="n">
-        <v>1661.635066864784</v>
+        <v>1429.242199108469</v>
       </c>
       <c r="BV2" t="n">
-        <v>27.54353640416047</v>
+        <v>25.61069836552749</v>
       </c>
       <c r="BW2" t="n">
-        <v>17.57087667161962</v>
+        <v>19.82763744427934</v>
       </c>
       <c r="BX2" t="n">
-        <v>36.09153046062407</v>
+        <v>36.35066864784547</v>
       </c>
       <c r="BY2" t="n">
-        <v>52.71263001485884</v>
+        <v>59.06983655274888</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.324219910846954</v>
+        <v>3.304606240713224</v>
       </c>
       <c r="CA2" t="n">
-        <v>17.57087667161962</v>
+        <v>13.63150074294205</v>
       </c>
       <c r="CB2" t="n">
-        <v>40.36552748885587</v>
+        <v>27.67607726597325</v>
       </c>
       <c r="CC2" t="n">
-        <v>139.1423476968797</v>
+        <v>105.7473997028232</v>
       </c>
       <c r="CD2" t="n">
-        <v>1416.117682020802</v>
+        <v>1207.420505200594</v>
       </c>
       <c r="CE2" t="n">
-        <v>1183.897176820208</v>
+        <v>1038.472511144131</v>
       </c>
       <c r="CF2" t="n">
-        <v>197.4111738484398</v>
+        <v>177.2508172362556</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.6243772879449737</v>
+        <v>0.2500472866615203</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.9713196810749013</v>
+        <v>0.7443712169028558</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.6212250695178668</v>
+        <v>0.3018630700651503</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.002452346364132</v>
+        <v>0.6855469196479596</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0759723907320837</v>
+        <v>0.07765789169311402</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.244309791792396</v>
+        <v>0.1885515539989192</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.974111738484398</v>
+        <v>1.772508172362556</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.35592675642007</v>
+        <v>1.208707883281145</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.1136907828002992</v>
+        <v>0.1240743822174355</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.403435290420579</v>
+        <v>1.239039553550643</v>
       </c>
       <c r="CQ2" t="n">
-        <v>1.364590638740451</v>
+        <v>1.199974169744449</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.09870751447049059</v>
+        <v>0.1026633070788765</v>
       </c>
       <c r="CS2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
         <v>0</v>
       </c>
       <c r="CX2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ2" t="n">
         <v>0</v>
       </c>
       <c r="DA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
         <v>1</v>
@@ -1889,7 +1889,7 @@
         <v>1</v>
       </c>
       <c r="DK2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL2" t="n">
         <v>1</v>
@@ -1898,52 +1898,52 @@
         <v>1</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ2" t="n">
         <v>1</v>
       </c>
       <c r="DR2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU2" t="n">
         <v>1</v>
       </c>
       <c r="DV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW2" t="n">
         <v>1</v>
       </c>
       <c r="DX2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY2" t="n">
         <v>1</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED2" t="n">
         <v>1</v>
@@ -1961,34 +1961,34 @@
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ2" t="n">
         <v>1</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
         <v>1</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP2" t="n">
         <v>0</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ES2" t="n">
         <v>1</v>
@@ -2009,10 +2009,10 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA2" t="n">
         <v>1</v>
@@ -2024,196 +2024,196 @@
         <v>1</v>
       </c>
       <c r="FD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>2.912332838038633</v>
+        <v>1.664190193164933</v>
       </c>
       <c r="FF2" t="n">
-        <v>5.30817236255572</v>
+        <v>3.819316493313522</v>
       </c>
       <c r="FG2" t="n">
-        <v>24.09093610698365</v>
+        <v>22.91589895988113</v>
       </c>
       <c r="FH2" t="n">
-        <v>9.799702823179791</v>
+        <v>9.336106983655275</v>
       </c>
       <c r="FI2" t="n">
-        <v>99.63031203566121</v>
+        <v>103.9702823179792</v>
       </c>
       <c r="FJ2" t="n">
-        <v>22.86597325408618</v>
+        <v>24.1890044576523</v>
       </c>
       <c r="FK2" t="n">
-        <v>9.391381872213966</v>
+        <v>8.911738484398217</v>
       </c>
       <c r="FL2" t="n">
-        <v>32.25735512630015</v>
+        <v>36.49569093610698</v>
       </c>
       <c r="FM2" t="n">
-        <v>1182.905794947994</v>
+        <v>1279.47102526003</v>
       </c>
       <c r="FN2" t="n">
-        <v>32.25735512630015</v>
+        <v>35.22258543833581</v>
       </c>
       <c r="FO2" t="n">
-        <v>17.96612184249629</v>
+        <v>11.03358098068351</v>
       </c>
       <c r="FP2" t="n">
-        <v>36.34056463595839</v>
+        <v>23.34026745913819</v>
       </c>
       <c r="FQ2" t="n">
-        <v>73.0894502228826</v>
+        <v>47.52927191679048</v>
       </c>
       <c r="FR2" t="n">
-        <v>2.449925705794948</v>
+        <v>3.819316493313522</v>
       </c>
       <c r="FS2" t="n">
-        <v>15.92451708766716</v>
+        <v>17.39910846953937</v>
       </c>
       <c r="FT2" t="n">
-        <v>46.14026745913819</v>
+        <v>41.16374442793462</v>
       </c>
       <c r="FU2" t="n">
-        <v>155.978603268945</v>
+        <v>147.2558692421991</v>
       </c>
       <c r="FV2" t="n">
-        <v>927.7052005943535</v>
+        <v>1068.984249628529</v>
       </c>
       <c r="FW2" t="n">
-        <v>725.1780089153045</v>
+        <v>843.2202080237741</v>
       </c>
       <c r="FX2" t="n">
-        <v>154.508647845468</v>
+        <v>165.3339673105498</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.4520639588247314</v>
+        <v>0.4177117384843982</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.8674837297422734</v>
+        <v>0.8712035661218426</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.3132462197360371</v>
+        <v>0.383900636263192</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.6407036098243161</v>
+        <v>1.191807063664419</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.07132568154133105</v>
+        <v>0.06845404474462628</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.3841753113799723</v>
+        <v>0.3171064530786014</v>
       </c>
       <c r="GE2" t="n">
-        <v>1.54508647845468</v>
+        <v>1.653339673105498</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.078171052377668</v>
+        <v>0.7538370099439936</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.1066615055296438</v>
+        <v>0.0926518371413937</v>
       </c>
       <c r="GH2" t="n">
-        <v>0.99588300091366</v>
+        <v>1.04171225652468</v>
       </c>
       <c r="GI2" t="n">
-        <v>1.01614042413796</v>
+        <v>1.023771506015646</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.09402739299057891</v>
+        <v>0.08515282659263136</v>
       </c>
       <c r="GK2" t="n">
-        <v>-0.5592867756315005</v>
+        <v>0.3114413075780083</v>
       </c>
       <c r="GL2" t="n">
-        <v>-2.246062407132246</v>
+        <v>12.19554234769688</v>
       </c>
       <c r="GM2" t="n">
-        <v>-0.3019316493313511</v>
+        <v>3.469242199108468</v>
       </c>
       <c r="GN2" t="n">
-        <v>40.93670133729572</v>
+        <v>20.36552748885586</v>
       </c>
       <c r="GO2" t="n">
-        <v>3.252897473997031</v>
+        <v>-3.948291233283804</v>
       </c>
       <c r="GP2" t="n">
-        <v>4.380386329866271</v>
+        <v>6.372065378900444</v>
       </c>
       <c r="GQ2" t="n">
-        <v>15.23150074294205</v>
+        <v>9.768796433878151</v>
       </c>
       <c r="GR2" t="n">
-        <v>478.7292719167906</v>
+        <v>149.7711738484395</v>
       </c>
       <c r="GS2" t="n">
-        <v>-4.713818722139674</v>
+        <v>-9.611887072808326</v>
       </c>
       <c r="GT2" t="n">
-        <v>-0.3952451708766702</v>
+        <v>8.794056463595837</v>
       </c>
       <c r="GU2" t="n">
-        <v>-0.249034175334323</v>
+        <v>13.01040118870728</v>
       </c>
       <c r="GV2" t="n">
-        <v>-20.37682020802377</v>
+        <v>11.5405646359584</v>
       </c>
       <c r="GW2" t="n">
-        <v>0.8742942050520059</v>
+        <v>-0.5147102526002976</v>
       </c>
       <c r="GX2" t="n">
-        <v>1.646359583952455</v>
+        <v>-3.767607726597326</v>
       </c>
       <c r="GY2" t="n">
-        <v>-5.774739970282319</v>
+        <v>-13.48766716196137</v>
       </c>
       <c r="GZ2" t="n">
-        <v>-16.83625557206537</v>
+        <v>-41.50846953937594</v>
       </c>
       <c r="HA2" t="n">
-        <v>488.4124814264487</v>
+        <v>138.4362555720654</v>
       </c>
       <c r="HB2" t="n">
-        <v>458.7191679049037</v>
+        <v>195.2523031203566</v>
       </c>
       <c r="HC2" t="n">
-        <v>42.9025260029718</v>
+        <v>11.91684992570578</v>
       </c>
       <c r="HD2" t="n">
-        <v>0.1723133291202423</v>
+        <v>-0.1676644518228779</v>
       </c>
       <c r="HE2" t="n">
-        <v>0.1038359513326279</v>
+        <v>-0.1268323492189868</v>
       </c>
       <c r="HF2" t="n">
-        <v>0.3079788497818298</v>
+        <v>-0.0820375661980417</v>
       </c>
       <c r="HG2" t="n">
-        <v>0.3617487365398157</v>
+        <v>-0.5062601440164591</v>
       </c>
       <c r="HH2" t="n">
-        <v>0.004646709190752649</v>
+        <v>0.009203846948487734</v>
       </c>
       <c r="HI2" t="n">
-        <v>-0.1398655195875763</v>
+        <v>-0.1285548990796821</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.429025260029718</v>
+        <v>0.1191684992570579</v>
       </c>
       <c r="HK2" t="n">
-        <v>0.2777557040424015</v>
+        <v>0.454870873337151</v>
       </c>
       <c r="HL2" t="n">
-        <v>0.007029277270655374</v>
+        <v>0.03142254507604179</v>
       </c>
       <c r="HM2" t="n">
-        <v>0.4075522895069194</v>
+        <v>0.197327297025963</v>
       </c>
       <c r="HN2" t="n">
-        <v>0.3484502146024915</v>
+        <v>0.1762026637288021</v>
       </c>
       <c r="HO2" t="n">
-        <v>0.004680121479911675</v>
+        <v>0.01751048048624516</v>
       </c>
     </row>
     <row r="3">
@@ -2227,28 +2227,28 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -2284,10 +2284,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -2299,25 +2299,25 @@
         <v>1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>1</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
         <v>1</v>
@@ -2344,22 +2344,22 @@
         <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -2368,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
@@ -2386,142 +2386,142 @@
         <v>1</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.864784546805349</v>
+        <v>1.939078751857355</v>
       </c>
       <c r="BN3" t="n">
-        <v>2.722734026745913</v>
+        <v>3.449034175334324</v>
       </c>
       <c r="BO3" t="n">
-        <v>24.05081723625557</v>
+        <v>29.56315007429421</v>
       </c>
       <c r="BP3" t="n">
-        <v>7.714413075780088</v>
+        <v>8.376225854383359</v>
       </c>
       <c r="BQ3" t="n">
-        <v>85.31233283803863</v>
+        <v>107.4127786032689</v>
       </c>
       <c r="BR3" t="n">
-        <v>25.41218424962853</v>
+        <v>28.0849925705795</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.714413075780088</v>
+        <v>9.361664190193165</v>
       </c>
       <c r="BT3" t="n">
-        <v>37.21069836552748</v>
+        <v>35.47578008915305</v>
       </c>
       <c r="BU3" t="n">
-        <v>1147.632392273403</v>
+        <v>1400.307875185736</v>
       </c>
       <c r="BV3" t="n">
-        <v>35.84933135215454</v>
+        <v>36.46121842496286</v>
       </c>
       <c r="BW3" t="n">
-        <v>18.15156017830609</v>
+        <v>23.15780089153046</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.58038632986627</v>
+        <v>36.95393759286776</v>
       </c>
       <c r="BY3" t="n">
-        <v>69.88350668647846</v>
+        <v>88.68945022288261</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.537890044576523</v>
+        <v>6.898068350668648</v>
       </c>
       <c r="CA3" t="n">
-        <v>22.23566121842497</v>
+        <v>20.20148588410104</v>
       </c>
       <c r="CB3" t="n">
-        <v>39.9334323922734</v>
+        <v>54.19910846953938</v>
       </c>
       <c r="CC3" t="n">
-        <v>169.717087667162</v>
+        <v>147.3230312035661</v>
       </c>
       <c r="CD3" t="n">
-        <v>882.6196136701337</v>
+        <v>1068.707875185736</v>
       </c>
       <c r="CE3" t="n">
-        <v>659.3554234769688</v>
+        <v>832.202674591382</v>
       </c>
       <c r="CF3" t="n">
-        <v>166.3136701337295</v>
+        <v>189.1056166419019</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.3453838533927687</v>
+        <v>0.2793310169927047</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.7462308073303615</v>
+        <v>0.6738768168564055</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.4092378392702942</v>
+        <v>0.4539246127307817</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.9090453848958578</v>
+        <v>1.073787979709997</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1018097892449949</v>
+        <v>0.08535351198491149</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.4812485362320186</v>
+        <v>0.3622764500901398</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.663136701337295</v>
+        <v>1.89105616641902</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.05807239758876</v>
+        <v>1.145046260165995</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.08708299747126189</v>
+        <v>0.1121887370693207</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.8550686264039808</v>
+        <v>1.07532372699256</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.910826801891725</v>
+        <v>1.122395037225311</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1246894202694899</v>
+        <v>0.1083538581419047</v>
       </c>
       <c r="CS3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV3" t="n">
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>1</v>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2551,16 +2551,16 @@
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>1</v>
@@ -2572,10 +2572,10 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
         <v>1</v>
@@ -2584,25 +2584,25 @@
         <v>0</v>
       </c>
       <c r="DS3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
         <v>1</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
         <v>1</v>
@@ -2611,19 +2611,19 @@
         <v>0</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
         <v>1</v>
       </c>
       <c r="EF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
         <v>1</v>
@@ -2635,19 +2635,19 @@
         <v>1</v>
       </c>
       <c r="EJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK3" t="n">
         <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
@@ -2662,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
@@ -2680,211 +2680,211 @@
         <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD3" t="n">
         <v>1</v>
       </c>
       <c r="FE3" t="n">
-        <v>1.797919762258544</v>
+        <v>2.421991084695394</v>
       </c>
       <c r="FF3" t="n">
-        <v>5.210104011887072</v>
+        <v>3.020505200594353</v>
       </c>
       <c r="FG3" t="n">
-        <v>43.9964338781575</v>
+        <v>38.40356612184249</v>
       </c>
       <c r="FH3" t="n">
-        <v>15.63031203566122</v>
+        <v>7.767013372956909</v>
       </c>
       <c r="FI3" t="n">
-        <v>135.4627043090639</v>
+        <v>116.9367013372957</v>
       </c>
       <c r="FJ3" t="n">
-        <v>33.57622585438335</v>
+        <v>22.86953937592867</v>
       </c>
       <c r="FK3" t="n">
-        <v>12.73580980683507</v>
+        <v>15.10252600297177</v>
       </c>
       <c r="FL3" t="n">
-        <v>52.67994056463595</v>
+        <v>63.86210995542348</v>
       </c>
       <c r="FM3" t="n">
-        <v>1689.810401188707</v>
+        <v>1273.790193164933</v>
       </c>
       <c r="FN3" t="n">
-        <v>42.2597325408618</v>
+        <v>32.36255572065379</v>
       </c>
       <c r="FO3" t="n">
-        <v>27.20832095096582</v>
+        <v>22.00653789004457</v>
       </c>
       <c r="FP3" t="n">
-        <v>45.73313521545319</v>
+        <v>53.07459138187222</v>
       </c>
       <c r="FQ3" t="n">
-        <v>86.83506686478454</v>
+        <v>46.60208023774145</v>
       </c>
       <c r="FR3" t="n">
-        <v>8.683506686478452</v>
+        <v>6.904011887072809</v>
       </c>
       <c r="FS3" t="n">
-        <v>19.1037147102526</v>
+        <v>14.67102526002972</v>
       </c>
       <c r="FT3" t="n">
-        <v>61.94234769687963</v>
+        <v>48.75958395245171</v>
       </c>
       <c r="FU3" t="n">
-        <v>216.5087667161961</v>
+        <v>192.0178306092125</v>
       </c>
       <c r="FV3" t="n">
-        <v>1340.154531946508</v>
+        <v>1022.65676077266</v>
       </c>
       <c r="FW3" t="n">
-        <v>1050.704309063893</v>
+        <v>757.2838038632987</v>
       </c>
       <c r="FX3" t="n">
-        <v>226.6974145616641</v>
+        <v>159.1806240713224</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.3070005983877148</v>
+        <v>0.1508446078048017</v>
       </c>
       <c r="FZ3" t="n">
-        <v>1.069175860994758</v>
+        <v>0.4165919714132743</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.7167338852331421</v>
+        <v>0.2809572221787753</v>
       </c>
       <c r="GB3" t="n">
-        <v>1.302526002971768</v>
+        <v>0.7088449206225073</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.1083054488970527</v>
+        <v>0.1352682547461879</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.4752855676008232</v>
+        <v>0.4082962168578272</v>
       </c>
       <c r="GE3" t="n">
-        <v>2.266974145616641</v>
+        <v>1.591806240713224</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.523125353674505</v>
+        <v>1.109245639332743</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.131919974840689</v>
+        <v>0.1393217301518303</v>
       </c>
       <c r="GH3" t="n">
-        <v>1.355300480526925</v>
+        <v>1.171836509174045</v>
       </c>
       <c r="GI3" t="n">
-        <v>1.37286159293342</v>
+        <v>1.120428820705934</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.1350428567957782</v>
+        <v>0.1677299859945257</v>
       </c>
       <c r="GK3" t="n">
-        <v>-2.487369985141159</v>
+        <v>0.428528974739971</v>
       </c>
       <c r="GL3" t="n">
-        <v>-19.94561664190192</v>
+        <v>-8.840416047548288</v>
       </c>
       <c r="GM3" t="n">
-        <v>-7.915898959881128</v>
+        <v>0.6092124814264492</v>
       </c>
       <c r="GN3" t="n">
-        <v>-50.15037147102524</v>
+        <v>-9.52392273402674</v>
       </c>
       <c r="GO3" t="n">
-        <v>-8.164041604754825</v>
+        <v>5.215453194650824</v>
       </c>
       <c r="GP3" t="n">
-        <v>-5.021396731054978</v>
+        <v>-5.740861812778602</v>
       </c>
       <c r="GQ3" t="n">
-        <v>-15.46924219910846</v>
+        <v>-28.38632986627043</v>
       </c>
       <c r="GR3" t="n">
-        <v>-542.1780089153042</v>
+        <v>126.5176820208026</v>
       </c>
       <c r="GS3" t="n">
-        <v>-6.410401188707269</v>
+        <v>4.098662704309071</v>
       </c>
       <c r="GT3" t="n">
-        <v>-9.056760772659729</v>
+        <v>1.151263001485891</v>
       </c>
       <c r="GU3" t="n">
-        <v>-12.15274888558692</v>
+        <v>-16.12065378900446</v>
       </c>
       <c r="GV3" t="n">
-        <v>-16.95156017830608</v>
+        <v>42.08736998514116</v>
       </c>
       <c r="GW3" t="n">
-        <v>-4.145616641901929</v>
+        <v>-0.005943536404160454</v>
       </c>
       <c r="GX3" t="n">
-        <v>3.131946508172369</v>
+        <v>5.530460624071322</v>
       </c>
       <c r="GY3" t="n">
-        <v>-22.00891530460623</v>
+        <v>5.439524517087676</v>
       </c>
       <c r="GZ3" t="n">
-        <v>-46.79167904903412</v>
+        <v>-44.69479940564634</v>
       </c>
       <c r="HA3" t="n">
-        <v>-457.5349182763741</v>
+        <v>46.05111441307599</v>
       </c>
       <c r="HB3" t="n">
-        <v>-391.3488855869241</v>
+        <v>74.91887072808333</v>
       </c>
       <c r="HC3" t="n">
-        <v>-60.38374442793457</v>
+        <v>29.92499257057952</v>
       </c>
       <c r="HD3" t="n">
-        <v>0.03838325500505385</v>
+        <v>0.1284864091879029</v>
       </c>
       <c r="HE3" t="n">
-        <v>-0.3229450536643964</v>
+        <v>0.2572848454431313</v>
       </c>
       <c r="HF3" t="n">
-        <v>-0.3074960459628479</v>
+        <v>0.1729673905520063</v>
       </c>
       <c r="HG3" t="n">
-        <v>-0.3934806180759102</v>
+        <v>0.3649430590874893</v>
       </c>
       <c r="HH3" t="n">
-        <v>-0.006495659652057742</v>
+        <v>-0.04991474276127637</v>
       </c>
       <c r="HI3" t="n">
-        <v>0.005962968631195331</v>
+        <v>-0.04601976676768743</v>
       </c>
       <c r="HJ3" t="n">
-        <v>-0.6038374442793459</v>
+        <v>0.2992499257057954</v>
       </c>
       <c r="HK3" t="n">
-        <v>-0.4650529560857444</v>
+        <v>0.03580062083325197</v>
       </c>
       <c r="HL3" t="n">
-        <v>-0.04483697736942707</v>
+        <v>-0.02713299308250967</v>
       </c>
       <c r="HM3" t="n">
-        <v>-0.5002318541229438</v>
+        <v>-0.09651278218148485</v>
       </c>
       <c r="HN3" t="n">
-        <v>-0.4620347910416948</v>
+        <v>0.001966216519377006</v>
       </c>
       <c r="HO3" t="n">
-        <v>-0.01035343652628827</v>
+        <v>-0.059376127852621</v>
       </c>
     </row>
     <row r="4">
@@ -2898,34 +2898,34 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
@@ -2937,13 +2937,13 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -2952,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
@@ -2961,13 +2961,13 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -2976,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -2988,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
         <v>1</v>
@@ -3006,25 +3006,25 @@
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
@@ -3033,28 +3033,28 @@
         <v>1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -3063,10 +3063,10 @@
         <v>1</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
@@ -3075,106 +3075,106 @@
         <v>1</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.087667161961367</v>
+        <v>1.300148588410104</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.043387815750372</v>
+        <v>0.9592867756315008</v>
       </c>
       <c r="BO4" t="n">
-        <v>22.17325408618128</v>
+        <v>24.46181277860327</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.217236255572065</v>
+        <v>7.674294205052006</v>
       </c>
       <c r="BQ4" t="n">
-        <v>110.4315007429421</v>
+        <v>109.3586924219911</v>
       </c>
       <c r="BR4" t="n">
-        <v>25.65141158989599</v>
+        <v>26.38038632986627</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.999702823179792</v>
+        <v>12.47072808320951</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.08558692421992</v>
+        <v>35.49361069836553</v>
       </c>
       <c r="BU4" t="n">
-        <v>1245.615156017831</v>
+        <v>1351.635066864784</v>
       </c>
       <c r="BV4" t="n">
-        <v>28.69479940564636</v>
+        <v>35.01396731054977</v>
       </c>
       <c r="BW4" t="n">
-        <v>19.12986627043091</v>
+        <v>18.70609212481426</v>
       </c>
       <c r="BX4" t="n">
-        <v>48.25943536404161</v>
+        <v>32.61575037147102</v>
       </c>
       <c r="BY4" t="n">
-        <v>63.9111441307578</v>
+        <v>66.6704309063893</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7.39108469539376</v>
+        <v>7.194650817236255</v>
       </c>
       <c r="CA4" t="n">
-        <v>13.91263001485884</v>
+        <v>14.86894502228826</v>
       </c>
       <c r="CB4" t="n">
-        <v>46.52035661218425</v>
+        <v>48.44398216939079</v>
       </c>
       <c r="CC4" t="n">
-        <v>171.2992570579495</v>
+        <v>167.8751857355126</v>
       </c>
       <c r="CD4" t="n">
-        <v>988.2315007429422</v>
+        <v>1087.351560178306</v>
       </c>
       <c r="CE4" t="n">
-        <v>741.717087667162</v>
+        <v>867.6748885586924</v>
       </c>
       <c r="CF4" t="n">
-        <v>160.5604457652303</v>
+        <v>191.7134621099555</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.3403970612514446</v>
+        <v>0.0599554234769688</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.5450148588410105</v>
+        <v>0.7138502087313382</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.5112464916625393</v>
+        <v>0.3333655899209609</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.798207033184745</v>
+        <v>0.9958982106958683</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.1027218141946309</v>
+        <v>0.07856166265152205</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.3936695583113815</v>
+        <v>0.3680808292698535</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.605604457652303</v>
+        <v>1.917134621099554</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.131168587584145</v>
+        <v>1.145309105178637</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.1146740385903754</v>
+        <v>0.1114296152204513</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.107007869946276</v>
+        <v>1.099336778536132</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.092687203130033</v>
+        <v>1.117755832699827</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1256598835083001</v>
+        <v>0.1059920819066047</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -3186,10 +3186,10 @@
         <v>0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>1</v>
       </c>
       <c r="DA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB4" t="n">
         <v>0</v>
@@ -3210,31 +3210,31 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK4" t="n">
         <v>1</v>
       </c>
       <c r="DL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
@@ -3252,19 +3252,19 @@
         <v>1</v>
       </c>
       <c r="DR4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW4" t="n">
         <v>1</v>
@@ -3282,16 +3282,16 @@
         <v>1</v>
       </c>
       <c r="EB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF4" t="n">
         <v>1</v>
@@ -3300,19 +3300,19 @@
         <v>1</v>
       </c>
       <c r="EH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK4" t="n">
         <v>0</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM4" t="n">
         <v>0</v>
@@ -3321,10 +3321,10 @@
         <v>1</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ4" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ4" t="n">
         <v>1</v>
       </c>
       <c r="FA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB4" t="n">
         <v>0</v>
@@ -3366,196 +3366,196 @@
         <v>0</v>
       </c>
       <c r="FD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>2.555720653789004</v>
+        <v>1.285289747399703</v>
       </c>
       <c r="FF4" t="n">
-        <v>3.961367013372957</v>
+        <v>2.420505200594353</v>
       </c>
       <c r="FG4" t="n">
-        <v>38.82139673105498</v>
+        <v>22.75274888558693</v>
       </c>
       <c r="FH4" t="n">
-        <v>14.26092124814265</v>
+        <v>8.713818722139672</v>
       </c>
       <c r="FI4" t="n">
-        <v>125.5753343239227</v>
+        <v>101.6612184249628</v>
       </c>
       <c r="FJ4" t="n">
-        <v>19.01456166419019</v>
+        <v>23.23684992570579</v>
       </c>
       <c r="FK4" t="n">
-        <v>15.84546805349183</v>
+        <v>8.713818722139672</v>
       </c>
       <c r="FL4" t="n">
-        <v>44.76344725111441</v>
+        <v>33.40297176820208</v>
       </c>
       <c r="FM4" t="n">
-        <v>1427.280534918277</v>
+        <v>1260.115007429421</v>
       </c>
       <c r="FN4" t="n">
-        <v>24.56047548291233</v>
+        <v>32.43476968796434</v>
       </c>
       <c r="FO4" t="n">
-        <v>16.24160475482912</v>
+        <v>21.30044576523031</v>
       </c>
       <c r="FP4" t="n">
-        <v>31.69093610698366</v>
+        <v>24.6891530460624</v>
       </c>
       <c r="FQ4" t="n">
-        <v>41.59435364041605</v>
+        <v>55.67161961367013</v>
       </c>
       <c r="FR4" t="n">
-        <v>3.961367013372957</v>
+        <v>3.872808320950966</v>
       </c>
       <c r="FS4" t="n">
-        <v>11.48796433878158</v>
+        <v>29.04606240713224</v>
       </c>
       <c r="FT4" t="n">
-        <v>29.71025260029718</v>
+        <v>41.63268945022288</v>
       </c>
       <c r="FU4" t="n">
-        <v>91.9037147102526</v>
+        <v>147.1667161961367</v>
       </c>
       <c r="FV4" t="n">
-        <v>1230.796731054978</v>
+        <v>998.2163447251113</v>
       </c>
       <c r="FW4" t="n">
-        <v>1069.569093610698</v>
+        <v>782.307280832095</v>
       </c>
       <c r="FX4" t="n">
-        <v>172.0817830609213</v>
+        <v>185.604338781575</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.2030094267400206</v>
+        <v>0.2737476119719804</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.7393125726214828</v>
+        <v>0.93592867756315</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.1980683506686479</v>
+        <v>0.3730140183077219</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.5710970777612678</v>
+        <v>0.7436407183503728</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.07195111902986841</v>
+        <v>0.08090777576182866</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.150890930304584</v>
+        <v>0.3906397606326836</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.720817830609212</v>
+        <v>1.856043387815751</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.201260146939898</v>
+        <v>1.06883786296196</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.1187999258027016</v>
+        <v>0.09471523933032616</v>
       </c>
       <c r="GH4" t="n">
-        <v>1.250666980367147</v>
+        <v>1.01757019718111</v>
       </c>
       <c r="GI4" t="n">
-        <v>1.19098538254649</v>
+        <v>1.057993338841476</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.09747733350979182</v>
+        <v>0.1039822349003727</v>
       </c>
       <c r="GK4" t="n">
-        <v>-0.9179791976225853</v>
+        <v>-1.461218424962853</v>
       </c>
       <c r="GL4" t="n">
-        <v>-16.6481426448737</v>
+        <v>1.709063893016342</v>
       </c>
       <c r="GM4" t="n">
-        <v>-9.043684992570579</v>
+        <v>-1.039524517087666</v>
       </c>
       <c r="GN4" t="n">
-        <v>-15.14383358098067</v>
+        <v>7.69747399702824</v>
       </c>
       <c r="GO4" t="n">
-        <v>6.6368499257058</v>
+        <v>3.143536404160475</v>
       </c>
       <c r="GP4" t="n">
-        <v>-5.845765230312036</v>
+        <v>3.756909361069837</v>
       </c>
       <c r="GQ4" t="n">
-        <v>1.322139673105504</v>
+        <v>2.09063893016345</v>
       </c>
       <c r="GR4" t="n">
-        <v>-181.6653789004458</v>
+        <v>91.52005943536392</v>
       </c>
       <c r="GS4" t="n">
-        <v>4.134323922734026</v>
+        <v>2.579197622585433</v>
       </c>
       <c r="GT4" t="n">
-        <v>2.888261515601787</v>
+        <v>-2.594353640416049</v>
       </c>
       <c r="GU4" t="n">
-        <v>16.56849925705795</v>
+        <v>7.926597325408618</v>
       </c>
       <c r="GV4" t="n">
-        <v>22.31679049034176</v>
+        <v>10.99881129271917</v>
       </c>
       <c r="GW4" t="n">
-        <v>3.429717682020803</v>
+        <v>3.321842496285289</v>
       </c>
       <c r="GX4" t="n">
-        <v>2.424665676077268</v>
+        <v>-14.17711738484398</v>
       </c>
       <c r="GY4" t="n">
-        <v>16.81010401188707</v>
+        <v>6.811292719167909</v>
       </c>
       <c r="GZ4" t="n">
-        <v>79.39554234769689</v>
+        <v>20.70846953937593</v>
       </c>
       <c r="HA4" t="n">
-        <v>-242.5652303120355</v>
+        <v>89.13521545319475</v>
       </c>
       <c r="HB4" t="n">
-        <v>-327.8520059435365</v>
+        <v>85.36760772659738</v>
       </c>
       <c r="HC4" t="n">
-        <v>-11.52133729569093</v>
+        <v>6.109123328380463</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.137387634511424</v>
+        <v>-0.2137921884950116</v>
       </c>
       <c r="HE4" t="n">
-        <v>-0.1942977137804722</v>
+        <v>-0.2220784688318118</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.3131781409938915</v>
+        <v>-0.03964842838676091</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.2271099554234771</v>
+        <v>0.2522574923454954</v>
       </c>
       <c r="HH4" t="n">
-        <v>0.03077069516476251</v>
+        <v>-0.002346113110306608</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.2427786280067975</v>
+        <v>-0.0225589313628301</v>
       </c>
       <c r="HJ4" t="n">
-        <v>-0.1152133729569089</v>
+        <v>0.06109123328380384</v>
       </c>
       <c r="HK4" t="n">
-        <v>-0.0700915593557534</v>
+        <v>0.07647124221667756</v>
       </c>
       <c r="HL4" t="n">
-        <v>-0.004125887212326165</v>
+        <v>0.01671437589012519</v>
       </c>
       <c r="HM4" t="n">
-        <v>-0.1436591104208704</v>
+        <v>0.08176658135502213</v>
       </c>
       <c r="HN4" t="n">
-        <v>-0.09829817941645658</v>
+        <v>0.05976249385835186</v>
       </c>
       <c r="HO4" t="n">
-        <v>0.02818254999850825</v>
+        <v>0.002009847006231941</v>
       </c>
     </row>
     <row r="5">
@@ -3563,55 +3563,55 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -3620,25 +3620,25 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>1</v>
@@ -3647,19 +3647,19 @@
         <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -3671,19 +3671,19 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
         <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -3695,16 +3695,16 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -3713,7 +3713,7 @@
         <v>1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>1</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
@@ -3746,118 +3746,118 @@
         <v>1</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>2.117384843982169</v>
+        <v>1.797919762258544</v>
       </c>
       <c r="BN5" t="n">
-        <v>2.999702823179792</v>
+        <v>5.204754829123329</v>
       </c>
       <c r="BO5" t="n">
-        <v>28.71144130757801</v>
+        <v>32.96344725111442</v>
       </c>
       <c r="BP5" t="n">
-        <v>8.570579494799405</v>
+        <v>14.45765230312036</v>
       </c>
       <c r="BQ5" t="n">
-        <v>99.41872213967309</v>
+        <v>135.9019316493313</v>
       </c>
       <c r="BR5" t="n">
-        <v>20.56939078751857</v>
+        <v>35.85497771173848</v>
       </c>
       <c r="BS5" t="n">
-        <v>11.14175334323923</v>
+        <v>9.831203566121841</v>
       </c>
       <c r="BT5" t="n">
-        <v>35.13937592867756</v>
+        <v>43.95126300148588</v>
       </c>
       <c r="BU5" t="n">
-        <v>1200.738187221397</v>
+        <v>1692.701931649331</v>
       </c>
       <c r="BV5" t="n">
-        <v>29.99702823179792</v>
+        <v>47.99940564635958</v>
       </c>
       <c r="BW5" t="n">
-        <v>21.42644873699851</v>
+        <v>27.18038632986627</v>
       </c>
       <c r="BX5" t="n">
-        <v>32.99673105497771</v>
+        <v>52.04754829123328</v>
       </c>
       <c r="BY5" t="n">
-        <v>70.27875185735512</v>
+        <v>102.9384843982169</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.285586924219911</v>
+        <v>6.93967310549777</v>
       </c>
       <c r="CA5" t="n">
-        <v>16.71263001485884</v>
+        <v>19.08410104011887</v>
       </c>
       <c r="CB5" t="n">
-        <v>41.99583952451709</v>
+        <v>61.87875185735512</v>
       </c>
       <c r="CC5" t="n">
-        <v>152.9848439821694</v>
+        <v>212.8166419019316</v>
       </c>
       <c r="CD5" t="n">
-        <v>944.9063893016345</v>
+        <v>1316.802971768202</v>
       </c>
       <c r="CE5" t="n">
-        <v>738.3554234769688</v>
+        <v>1025.336701337296</v>
       </c>
       <c r="CF5" t="n">
-        <v>166.7406240713225</v>
+        <v>225.0767310549777</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.2172108286783577</v>
+        <v>0.5481758587536054</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.6215143304383755</v>
+        <v>1.385828744573609</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.294245377470183</v>
+        <v>0.581059930658742</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.6275911593868939</v>
+        <v>1.137335314512135</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.07947684154185765</v>
+        <v>0.09310048758609291</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.354050965416743</v>
+        <v>0.4743378433463509</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.667406240713224</v>
+        <v>2.250767310549777</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.043408871915625</v>
+        <v>1.55707159314448</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1014273772342032</v>
+        <v>0.1493177406243898</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.9936839092567212</v>
+        <v>1.35694417946569</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.015031478055592</v>
+        <v>1.383453126612227</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1051455032226973</v>
+        <v>0.1146456225118744</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ5" t="n">
         <v>1</v>
@@ -3881,46 +3881,46 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
       </c>
       <c r="DG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
         <v>1</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DJ5" t="n">
         <v>1</v>
       </c>
       <c r="DK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
         <v>1</v>
       </c>
       <c r="DP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
         <v>1</v>
@@ -3929,16 +3929,16 @@
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV5" t="n">
         <v>1</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX5" t="n">
         <v>1</v>
@@ -3956,10 +3956,10 @@
         <v>1</v>
       </c>
       <c r="EC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>1</v>
@@ -3971,31 +3971,31 @@
         <v>0</v>
       </c>
       <c r="EH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
         <v>1</v>
       </c>
       <c r="EM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO5" t="n">
         <v>1</v>
       </c>
       <c r="EP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ5" t="n">
         <v>1</v>
@@ -4007,19 +4007,19 @@
         <v>0</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
         <v>0</v>
@@ -4031,7 +4031,7 @@
         <v>1</v>
       </c>
       <c r="FB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC5" t="n">
         <v>0</v>
@@ -4040,193 +4040,193 @@
         <v>1</v>
       </c>
       <c r="FE5" t="n">
-        <v>1.567607726597325</v>
+        <v>4.145616641901932</v>
       </c>
       <c r="FF5" t="n">
-        <v>3.99851411589896</v>
+        <v>7.578008915304606</v>
       </c>
       <c r="FG5" t="n">
-        <v>39.09658246656761</v>
+        <v>37.13224368499257</v>
       </c>
       <c r="FH5" t="n">
-        <v>12.43982169390788</v>
+        <v>16.67161961367013</v>
       </c>
       <c r="FI5" t="n">
-        <v>114.1797919762259</v>
+        <v>120.4903417533432</v>
       </c>
       <c r="FJ5" t="n">
-        <v>29.3224368499257</v>
+        <v>17.05052005943536</v>
       </c>
       <c r="FK5" t="n">
-        <v>13.77265973254086</v>
+        <v>8.714710252600296</v>
       </c>
       <c r="FL5" t="n">
-        <v>52.42496285289748</v>
+        <v>28.03863298662704</v>
       </c>
       <c r="FM5" t="n">
-        <v>1291.075780089153</v>
+        <v>1534.546805349183</v>
       </c>
       <c r="FN5" t="n">
-        <v>29.7667161961367</v>
+        <v>23.11292719167905</v>
       </c>
       <c r="FO5" t="n">
-        <v>11.55126300148589</v>
+        <v>13.64041604754829</v>
       </c>
       <c r="FP5" t="n">
-        <v>47.53789004457652</v>
+        <v>13.64041604754829</v>
       </c>
       <c r="FQ5" t="n">
-        <v>78.63744427934621</v>
+        <v>34.10104011887073</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.4442793462109956</v>
+        <v>2.652303120356612</v>
       </c>
       <c r="FS5" t="n">
-        <v>18.21545319465082</v>
+        <v>10.60921248142645</v>
       </c>
       <c r="FT5" t="n">
-        <v>50.6478454680535</v>
+        <v>31.44873699851412</v>
       </c>
       <c r="FU5" t="n">
-        <v>170.6032689450223</v>
+        <v>100.408618127786</v>
       </c>
       <c r="FV5" t="n">
-        <v>1036.059435364042</v>
+        <v>1332.592867756315</v>
       </c>
       <c r="FW5" t="n">
-        <v>795.704309063893</v>
+        <v>1180.653789004458</v>
       </c>
       <c r="FX5" t="n">
-        <v>171.0031203566122</v>
+        <v>167.3224368499257</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.2343487757568695</v>
+        <v>0.4065345384263034</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.6721084958863218</v>
+        <v>0.844810298405747</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.2221396731054978</v>
+        <v>0.07578008915304606</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.5003014128933031</v>
+        <v>0.4978330856859831</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.1098363368315027</v>
+        <v>0.03986080110755632</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.367750292370141</v>
+        <v>0.1487962279710546</v>
       </c>
       <c r="GE5" t="n">
-        <v>1.710031203566122</v>
+        <v>1.673224368499257</v>
       </c>
       <c r="GF5" t="n">
-        <v>1.035818469636917</v>
+        <v>0.907088475406842</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.0966393873655737</v>
+        <v>0.09267012581067258</v>
       </c>
       <c r="GH5" t="n">
-        <v>1.140997278762056</v>
+        <v>1.208124089870607</v>
       </c>
       <c r="GI5" t="n">
-        <v>1.140276502354006</v>
+        <v>1.154703061650861</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.1387393724258594</v>
+        <v>0.05249007335492289</v>
       </c>
       <c r="GK5" t="n">
-        <v>-0.9988112927191688</v>
+        <v>-2.373254086181277</v>
       </c>
       <c r="GL5" t="n">
-        <v>-10.3851411589896</v>
+        <v>-4.168796433878157</v>
       </c>
       <c r="GM5" t="n">
-        <v>-3.86924219910847</v>
+        <v>-2.213967310549778</v>
       </c>
       <c r="GN5" t="n">
-        <v>-14.76106983655276</v>
+        <v>15.4115898959881</v>
       </c>
       <c r="GO5" t="n">
-        <v>-8.753046062407133</v>
+        <v>18.80445765230312</v>
       </c>
       <c r="GP5" t="n">
-        <v>-2.630906389301636</v>
+        <v>1.116493313521545</v>
       </c>
       <c r="GQ5" t="n">
-        <v>-17.28558692421992</v>
+        <v>15.91263001485884</v>
       </c>
       <c r="GR5" t="n">
-        <v>-90.33759286775648</v>
+        <v>158.1551263001486</v>
       </c>
       <c r="GS5" t="n">
-        <v>0.2303120356612176</v>
+        <v>24.88647845468054</v>
       </c>
       <c r="GT5" t="n">
-        <v>9.875185735512627</v>
+        <v>13.53997028231798</v>
       </c>
       <c r="GU5" t="n">
-        <v>-14.54115898959881</v>
+        <v>38.40713224368499</v>
       </c>
       <c r="GV5" t="n">
-        <v>-8.358692421991094</v>
+        <v>68.83744427934622</v>
       </c>
       <c r="GW5" t="n">
-        <v>0.8413075780089152</v>
+        <v>4.287369985141158</v>
       </c>
       <c r="GX5" t="n">
-        <v>-1.502823179791978</v>
+        <v>8.474888558692422</v>
       </c>
       <c r="GY5" t="n">
-        <v>-8.652005943536409</v>
+        <v>30.430014858841</v>
       </c>
       <c r="GZ5" t="n">
-        <v>-17.61842496285288</v>
+        <v>112.4080237741456</v>
       </c>
       <c r="HA5" t="n">
-        <v>-91.15304606240704</v>
+        <v>-15.7898959881129</v>
       </c>
       <c r="HB5" t="n">
-        <v>-57.34888558692421</v>
+        <v>-155.3170876671618</v>
       </c>
       <c r="HC5" t="n">
-        <v>-4.2624962852897</v>
+        <v>57.75429420505202</v>
       </c>
       <c r="HD5" t="n">
-        <v>-0.01713794707851177</v>
+        <v>0.141641320327302</v>
       </c>
       <c r="HE5" t="n">
-        <v>-0.05059416544794637</v>
+        <v>0.5410184461678625</v>
       </c>
       <c r="HF5" t="n">
-        <v>0.07210570436468527</v>
+        <v>0.5052798415056959</v>
       </c>
       <c r="HG5" t="n">
-        <v>0.1272897464935908</v>
+        <v>0.6395022288261515</v>
       </c>
       <c r="HH5" t="n">
-        <v>-0.03035949528964502</v>
+        <v>0.05323968647853659</v>
       </c>
       <c r="HI5" t="n">
-        <v>-0.01369932695339804</v>
+        <v>0.3255416153752962</v>
       </c>
       <c r="HJ5" t="n">
-        <v>-0.04262496285289719</v>
+        <v>0.57754294205052</v>
       </c>
       <c r="HK5" t="n">
-        <v>0.00759040227870833</v>
+        <v>0.6499831177376376</v>
       </c>
       <c r="HL5" t="n">
-        <v>0.004787989868629453</v>
+        <v>0.05664761481371719</v>
       </c>
       <c r="HM5" t="n">
-        <v>-0.1473133695053349</v>
+        <v>0.1488200895950826</v>
       </c>
       <c r="HN5" t="n">
-        <v>-0.1252450242984147</v>
+        <v>0.2287500649613661</v>
       </c>
       <c r="HO5" t="n">
-        <v>-0.03359386920316207</v>
+        <v>0.06215554915695151</v>
       </c>
     </row>
     <row r="6">
@@ -4237,10 +4237,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -4252,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -4264,76 +4264,76 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="n">
         <v>1</v>
@@ -4348,22 +4348,22 @@
         <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
@@ -4372,40 +4372,40 @@
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY6" t="n">
         <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
         <v>1</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -4414,112 +4414,112 @@
         <v>1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK6" t="n">
         <v>1</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.421991084695394</v>
+        <v>2.236255572065379</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.566121842496285</v>
+        <v>5.784249628528975</v>
       </c>
       <c r="BO6" t="n">
-        <v>39.22734026745913</v>
+        <v>31.33135215453195</v>
       </c>
       <c r="BP6" t="n">
-        <v>8.469539375928676</v>
+        <v>12.05052005943536</v>
       </c>
       <c r="BQ6" t="n">
-        <v>124.3684992570579</v>
+        <v>116.1670133729569</v>
       </c>
       <c r="BR6" t="n">
-        <v>22.73402674591381</v>
+        <v>22.17295690936107</v>
       </c>
       <c r="BS6" t="n">
-        <v>17.83060921248142</v>
+        <v>11.08647845468053</v>
       </c>
       <c r="BT6" t="n">
-        <v>69.09361069836551</v>
+        <v>34.70549777117385</v>
       </c>
       <c r="BU6" t="n">
-        <v>1353.34323922734</v>
+        <v>1477.875780089153</v>
       </c>
       <c r="BV6" t="n">
-        <v>32.09509658246656</v>
+        <v>42.41783060921248</v>
       </c>
       <c r="BW6" t="n">
-        <v>21.84249628528974</v>
+        <v>19.28083209509658</v>
       </c>
       <c r="BX6" t="n">
-        <v>52.15453194650816</v>
+        <v>25.54710252600297</v>
       </c>
       <c r="BY6" t="n">
-        <v>49.92570579494798</v>
+        <v>63.62674591381872</v>
       </c>
       <c r="BZ6" t="n">
-        <v>6.686478454680534</v>
+        <v>3.374145616641901</v>
       </c>
       <c r="CA6" t="n">
-        <v>14.71025260029717</v>
+        <v>24.10104011887073</v>
       </c>
       <c r="CB6" t="n">
-        <v>49.92570579494798</v>
+        <v>45.30995542347697</v>
       </c>
       <c r="CC6" t="n">
-        <v>201.4858841010401</v>
+        <v>144.1242199108469</v>
       </c>
       <c r="CD6" t="n">
-        <v>1101.48588410104</v>
+        <v>1213.246359583952</v>
       </c>
       <c r="CE6" t="n">
-        <v>831.3521545319463</v>
+        <v>991.9988112927192</v>
       </c>
       <c r="CF6" t="n">
-        <v>167.2511144130758</v>
+        <v>197.0501040118871</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1929783089359221</v>
+        <v>0.5156161916340223</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.4732256482080521</v>
+        <v>0.9948199893222182</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.3225043901121167</v>
+        <v>0.2907427061959008</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.7733351344049708</v>
+        <v>0.6494394728773394</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.1412159379521177</v>
+        <v>0.06665990011960654</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.4133018647874209</v>
+        <v>0.2839948476341436</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.672511144130758</v>
+        <v>1.970501040118871</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.11407454307234</v>
+        <v>1.214998466944975</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1417191513075549</v>
+        <v>0.1147350069474067</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.243860249241448</v>
+        <v>1.16239565807434</v>
       </c>
       <c r="CQ6" t="n">
-        <v>1.18797820290708</v>
+        <v>1.161994319388282</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1779829022216694</v>
+        <v>0.08774129361844031</v>
       </c>
       <c r="CS6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
@@ -4534,31 +4534,31 @@
         <v>1</v>
       </c>
       <c r="CX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB6" t="n">
         <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD6" t="n">
         <v>1</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
@@ -4570,13 +4570,13 @@
         <v>1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM6" t="n">
         <v>1</v>
@@ -4585,16 +4585,16 @@
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV6" t="n">
         <v>1</v>
@@ -4612,19 +4612,19 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC6" t="n">
         <v>0</v>
@@ -4633,10 +4633,10 @@
         <v>1</v>
       </c>
       <c r="EE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>0</v>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -4690,13 +4690,13 @@
         <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY6" t="n">
         <v>0</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA6" t="n">
         <v>0</v>
@@ -4705,204 +4705,204 @@
         <v>1</v>
       </c>
       <c r="FC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FD6" t="n">
         <v>1</v>
       </c>
       <c r="FE6" t="n">
-        <v>2.555720653789004</v>
+        <v>2.087667161961367</v>
       </c>
       <c r="FF6" t="n">
-        <v>4.023179791976226</v>
+        <v>3.202377414561664</v>
       </c>
       <c r="FG6" t="n">
-        <v>36.20861812778603</v>
+        <v>22.81693907875186</v>
       </c>
       <c r="FH6" t="n">
-        <v>12.06953937592868</v>
+        <v>5.604160475482912</v>
       </c>
       <c r="FI6" t="n">
-        <v>135.0638930163447</v>
+        <v>106.8793462109955</v>
       </c>
       <c r="FJ6" t="n">
-        <v>29.31173848439822</v>
+        <v>22.81693907875186</v>
       </c>
       <c r="FK6" t="n">
-        <v>11.49479940564636</v>
+        <v>10.40772659732541</v>
       </c>
       <c r="FL6" t="n">
-        <v>33.90965824665676</v>
+        <v>50.83774145616641</v>
       </c>
       <c r="FM6" t="n">
-        <v>1692.609212481427</v>
+        <v>1176.873699851412</v>
       </c>
       <c r="FN6" t="n">
-        <v>40.23179791976226</v>
+        <v>24.41812778603269</v>
       </c>
       <c r="FO6" t="n">
-        <v>17.24219910846954</v>
+        <v>17.21277860326894</v>
       </c>
       <c r="FP6" t="n">
-        <v>30.46121842496285</v>
+        <v>47.63536404160476</v>
       </c>
       <c r="FQ6" t="n">
-        <v>80.46359583952452</v>
+        <v>59.24398216939079</v>
       </c>
       <c r="FR6" t="n">
-        <v>4.023179791976226</v>
+        <v>6.00445765230312</v>
       </c>
       <c r="FS6" t="n">
-        <v>25.28855869242199</v>
+        <v>12.00891530460624</v>
       </c>
       <c r="FT6" t="n">
-        <v>45.40445765230312</v>
+        <v>43.63239227340268</v>
       </c>
       <c r="FU6" t="n">
-        <v>151.1566121842496</v>
+        <v>158.9179791976226</v>
       </c>
       <c r="FV6" t="n">
-        <v>1358.110549777118</v>
+        <v>945.1016344725111</v>
       </c>
       <c r="FW6" t="n">
-        <v>1110.397622585438</v>
+        <v>712.5289747399703</v>
       </c>
       <c r="FX6" t="n">
-        <v>233.6317979197622</v>
+        <v>149.3108469539376</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.4197114256666928</v>
+        <v>0.2914129233817198</v>
       </c>
       <c r="FZ6" t="n">
-        <v>1.133094809832903</v>
+        <v>0.4842056234998285</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.3826558223195433</v>
+        <v>0.3677766413873397</v>
       </c>
       <c r="GB6" t="n">
-        <v>1.194566058534151</v>
+        <v>0.689169641651068</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.06876810570714578</v>
+        <v>0.1120997793266874</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.3289935151082242</v>
+        <v>0.3465263862424381</v>
       </c>
       <c r="GE6" t="n">
-        <v>2.336317979197622</v>
+        <v>1.493108469539376</v>
       </c>
       <c r="GF6" t="n">
-        <v>1.393931031821076</v>
+        <v>1.062707092807572</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.1117832345019056</v>
+        <v>0.1072909618970283</v>
       </c>
       <c r="GH6" t="n">
-        <v>1.35147661341485</v>
+        <v>1.071525470448408</v>
       </c>
       <c r="GI6" t="n">
-        <v>1.372408946263219</v>
+        <v>1.039505294809903</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.09323925172273551</v>
+        <v>0.1350692232513773</v>
       </c>
       <c r="GK6" t="n">
-        <v>-0.4570579494799407</v>
+        <v>2.58187221396731</v>
       </c>
       <c r="GL6" t="n">
-        <v>3.018722139673102</v>
+        <v>8.514413075780087</v>
       </c>
       <c r="GM6" t="n">
-        <v>-3.600000000000001</v>
+        <v>6.446359583952452</v>
       </c>
       <c r="GN6" t="n">
-        <v>-10.69539375928682</v>
+        <v>9.28766716196138</v>
       </c>
       <c r="GO6" t="n">
-        <v>-6.577711738484403</v>
+        <v>-0.6439821693907923</v>
       </c>
       <c r="GP6" t="n">
-        <v>6.335809806835064</v>
+        <v>0.6787518573551239</v>
       </c>
       <c r="GQ6" t="n">
-        <v>35.18395245170875</v>
+        <v>-16.13224368499257</v>
       </c>
       <c r="GR6" t="n">
-        <v>-339.2659732540865</v>
+        <v>301.0020802377414</v>
       </c>
       <c r="GS6" t="n">
-        <v>-8.136701337295698</v>
+        <v>17.99970282317979</v>
       </c>
       <c r="GT6" t="n">
-        <v>4.600297176820206</v>
+        <v>2.068053491827637</v>
       </c>
       <c r="GU6" t="n">
-        <v>21.69331352154531</v>
+        <v>-22.08826151560179</v>
       </c>
       <c r="GV6" t="n">
-        <v>-30.53789004457654</v>
+        <v>4.382763744427926</v>
       </c>
       <c r="GW6" t="n">
-        <v>2.663298662704308</v>
+        <v>-2.630312035661219</v>
       </c>
       <c r="GX6" t="n">
-        <v>-10.57830609212482</v>
+        <v>12.09212481426449</v>
       </c>
       <c r="GY6" t="n">
-        <v>4.521248142644858</v>
+        <v>1.677563150074292</v>
       </c>
       <c r="GZ6" t="n">
-        <v>50.32927191679045</v>
+        <v>-14.79375928677567</v>
       </c>
       <c r="HA6" t="n">
-        <v>-256.6246656760777</v>
+        <v>268.1447251114413</v>
       </c>
       <c r="HB6" t="n">
-        <v>-279.045468053492</v>
+        <v>279.4698365527489</v>
       </c>
       <c r="HC6" t="n">
-        <v>-66.38068350668649</v>
+        <v>47.73925705794952</v>
       </c>
       <c r="HD6" t="n">
-        <v>-0.2267331167307707</v>
+        <v>0.2242032682523025</v>
       </c>
       <c r="HE6" t="n">
-        <v>-0.6598691616248509</v>
+        <v>0.5106143658223896</v>
       </c>
       <c r="HF6" t="n">
-        <v>-0.06015143220742658</v>
+        <v>-0.07703393519143886</v>
       </c>
       <c r="HG6" t="n">
-        <v>-0.4212309241291801</v>
+        <v>-0.03973016877372859</v>
       </c>
       <c r="HH6" t="n">
-        <v>0.07244783224497195</v>
+        <v>-0.0454398792070809</v>
       </c>
       <c r="HI6" t="n">
-        <v>0.08430834967919676</v>
+        <v>-0.06253153860829452</v>
       </c>
       <c r="HJ6" t="n">
-        <v>-0.6638068350668647</v>
+        <v>0.4773925705794946</v>
       </c>
       <c r="HK6" t="n">
-        <v>-0.2798564887487365</v>
+        <v>0.1522913741374032</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.02993591680564929</v>
+        <v>0.007444045050378406</v>
       </c>
       <c r="HM6" t="n">
-        <v>-0.1076163641734016</v>
+        <v>0.09087018762593146</v>
       </c>
       <c r="HN6" t="n">
-        <v>-0.1844307433561392</v>
+        <v>0.122489024578379</v>
       </c>
       <c r="HO6" t="n">
-        <v>0.0847436504989339</v>
+        <v>-0.04732792963293699</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -4911,19 +4911,19 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4932,10 +4932,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -4950,34 +4950,34 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -4986,19 +4986,19 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>1</v>
@@ -5010,10 +5010,10 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="n">
         <v>1</v>
@@ -5022,10 +5022,10 @@
         <v>1</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -5046,163 +5046,163 @@
         <v>1</v>
       </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
       <c r="BH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI7" t="n">
         <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.285289747399703</v>
+        <v>2.555720653789004</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.980683506686478</v>
+        <v>2.528974739970283</v>
       </c>
       <c r="BO7" t="n">
-        <v>20.99524517087667</v>
+        <v>37.42882615156019</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.922734026745912</v>
+        <v>9.104309063893018</v>
       </c>
       <c r="BQ7" t="n">
-        <v>91.50757800891529</v>
+        <v>121.8965824665676</v>
       </c>
       <c r="BR7" t="n">
-        <v>20.20297176820208</v>
+        <v>26.807132243685</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.526597325408616</v>
+        <v>11.6332838038633</v>
       </c>
       <c r="BT7" t="n">
-        <v>31.69093610698365</v>
+        <v>31.35928677563151</v>
       </c>
       <c r="BU7" t="n">
-        <v>1099.675482912333</v>
+        <v>1520.925408618128</v>
       </c>
       <c r="BV7" t="n">
-        <v>27.72956909361069</v>
+        <v>34.39405646359585</v>
       </c>
       <c r="BW7" t="n">
-        <v>14.26092124814264</v>
+        <v>21.74918276374443</v>
       </c>
       <c r="BX7" t="n">
-        <v>26.54115898959881</v>
+        <v>34.39405646359585</v>
       </c>
       <c r="BY7" t="n">
-        <v>49.12095096582465</v>
+        <v>88.51411589895989</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.772956909361069</v>
+        <v>3.034769687964339</v>
       </c>
       <c r="CA7" t="n">
-        <v>23.76820208023774</v>
+        <v>22.76077265973255</v>
       </c>
       <c r="CB7" t="n">
-        <v>38.82139673105497</v>
+        <v>39.95780089153047</v>
       </c>
       <c r="CC7" t="n">
-        <v>129.932838038633</v>
+        <v>135.0472511144131</v>
       </c>
       <c r="CD7" t="n">
-        <v>875.0659732540861</v>
+        <v>1194.687667161961</v>
       </c>
       <c r="CE7" t="n">
-        <v>686.108766716196</v>
+        <v>968.0915304606242</v>
       </c>
       <c r="CF7" t="n">
-        <v>153.2652897473997</v>
+        <v>203.3801485884101</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.2240058727800184</v>
+        <v>0.206311097208102</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.7988756810302128</v>
+        <v>0.6976864523865386</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.2586306032540489</v>
+        <v>0.2608837100179871</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.506985480044837</v>
+        <v>0.9773436677761382</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0730262373513044</v>
+        <v>0.06438289322266191</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.3077593386872008</v>
+        <v>0.294853591165442</v>
       </c>
       <c r="CM7" t="n">
-        <v>1.532652897473997</v>
+        <v>2.033801485884101</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.8567329580805013</v>
+        <v>1.26284517859555</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.08325599395354144</v>
+        <v>0.1137124795114872</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.9167896725038489</v>
+        <v>1.217388023604609</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.9393046981845591</v>
+        <v>1.245329774188884</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.09031176049416183</v>
+        <v>0.08976646172323798</v>
       </c>
       <c r="CS7" t="n">
         <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -5211,31 +5211,31 @@
         <v>1</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC7" t="n">
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG7" t="n">
         <v>1</v>
       </c>
       <c r="DH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
@@ -5256,22 +5256,22 @@
         <v>1</v>
       </c>
       <c r="DO7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
@@ -5283,16 +5283,16 @@
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB7" t="n">
         <v>1</v>
@@ -5307,19 +5307,19 @@
         <v>1</v>
       </c>
       <c r="EF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
         <v>0</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EI7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK7" t="n">
         <v>1</v>
@@ -5337,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="EP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ7" t="n">
         <v>1</v>
@@ -5352,22 +5352,22 @@
         <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>1</v>
       </c>
       <c r="EW7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA7" t="n">
         <v>1</v>
@@ -5379,204 +5379,204 @@
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FE7" t="n">
-        <v>3.328380386329866</v>
+        <v>1.567607726597325</v>
       </c>
       <c r="FF7" t="n">
-        <v>6.865676077265973</v>
+        <v>5.206537890044576</v>
       </c>
       <c r="FG7" t="n">
-        <v>22.61634472511144</v>
+        <v>36.01188707280832</v>
       </c>
       <c r="FH7" t="n">
-        <v>10.90430906389302</v>
+        <v>12.58246656760772</v>
       </c>
       <c r="FI7" t="n">
-        <v>112.6778603268945</v>
+        <v>106.7340267459138</v>
       </c>
       <c r="FJ7" t="n">
-        <v>23.82793462109955</v>
+        <v>29.06983655274889</v>
       </c>
       <c r="FK7" t="n">
-        <v>6.865676077265973</v>
+        <v>12.14858841010401</v>
       </c>
       <c r="FL7" t="n">
-        <v>26.65497771173848</v>
+        <v>48.16047548291233</v>
       </c>
       <c r="FM7" t="n">
-        <v>1447.849925705795</v>
+        <v>1200.540861812779</v>
       </c>
       <c r="FN7" t="n">
-        <v>26.25111441307578</v>
+        <v>26.46656760772659</v>
       </c>
       <c r="FO7" t="n">
-        <v>16.15453194650817</v>
+        <v>11.7147102526003</v>
       </c>
       <c r="FP7" t="n">
-        <v>24.23179791976226</v>
+        <v>40.35066864784547</v>
       </c>
       <c r="FQ7" t="n">
-        <v>66.2335809806835</v>
+        <v>79.83358098068349</v>
       </c>
       <c r="FR7" t="n">
-        <v>2.82704309063893</v>
+        <v>0.8677563150074294</v>
       </c>
       <c r="FS7" t="n">
-        <v>12.92362555720654</v>
+        <v>19.95839524517087</v>
       </c>
       <c r="FT7" t="n">
-        <v>35.13610698365527</v>
+        <v>46.42496285289747</v>
       </c>
       <c r="FU7" t="n">
-        <v>105.8121842496285</v>
+        <v>165.3075780089153</v>
       </c>
       <c r="FV7" t="n">
-        <v>1203.512630014859</v>
+        <v>954.965824665676</v>
       </c>
       <c r="FW7" t="n">
-        <v>1043.178900445765</v>
+        <v>739.7622585438336</v>
       </c>
       <c r="FX7" t="n">
-        <v>173.2977414561664</v>
+        <v>168.2579494799405</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.6768935373690202</v>
+        <v>0.3218362404622347</v>
       </c>
       <c r="FZ7" t="n">
-        <v>1.086584589259181</v>
+        <v>0.7444540425923172</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.1636709157738328</v>
+        <v>0.3099129696455105</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.8312047747357045</v>
+        <v>0.6745364525727394</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.04205233981580161</v>
+        <v>0.1070970266346925</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.1889736196516494</v>
+        <v>0.3742549357457919</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.732977414561664</v>
+        <v>1.682579494799405</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.079128865836664</v>
+        <v>1.006609931395303</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.09639550687121608</v>
+        <v>0.08616934155173529</v>
       </c>
       <c r="GH7" t="n">
-        <v>1.128470214664908</v>
+        <v>1.06633655312986</v>
       </c>
       <c r="GI7" t="n">
-        <v>1.124610422041764</v>
+        <v>1.074549353485142</v>
       </c>
       <c r="GJ7" t="n">
-        <v>0.05243199175654027</v>
+        <v>0.1339422996821367</v>
       </c>
       <c r="GK7" t="n">
-        <v>-4.884992570579495</v>
+        <v>-2.677563150074293</v>
       </c>
       <c r="GL7" t="n">
-        <v>-1.621099554234771</v>
+        <v>1.416939078751867</v>
       </c>
       <c r="GM7" t="n">
-        <v>-2.981575037147104</v>
+        <v>-3.478157503714707</v>
       </c>
       <c r="GN7" t="n">
-        <v>-21.1702823179792</v>
+        <v>15.16255572065381</v>
       </c>
       <c r="GO7" t="n">
-        <v>-3.624962852897479</v>
+        <v>-2.262704309063889</v>
       </c>
       <c r="GP7" t="n">
-        <v>0.6609212481426434</v>
+        <v>-0.5153046062407096</v>
       </c>
       <c r="GQ7" t="n">
-        <v>5.035958395245167</v>
+        <v>-16.80118870728082</v>
       </c>
       <c r="GR7" t="n">
-        <v>-348.1744427934623</v>
+        <v>320.3845468053494</v>
       </c>
       <c r="GS7" t="n">
-        <v>1.478454680534913</v>
+        <v>7.927488855869253</v>
       </c>
       <c r="GT7" t="n">
-        <v>-1.89361069836553</v>
+        <v>10.03447251114413</v>
       </c>
       <c r="GU7" t="n">
-        <v>2.309361069836548</v>
+        <v>-5.956612184249622</v>
       </c>
       <c r="GV7" t="n">
-        <v>-17.11263001485884</v>
+        <v>8.680534918276393</v>
       </c>
       <c r="GW7" t="n">
-        <v>-0.05408618127786058</v>
+        <v>2.16701337295691</v>
       </c>
       <c r="GX7" t="n">
-        <v>10.8445765230312</v>
+        <v>2.802377414561672</v>
       </c>
       <c r="GY7" t="n">
-        <v>3.685289747399707</v>
+        <v>-6.467161961366998</v>
       </c>
       <c r="GZ7" t="n">
-        <v>24.12065378900444</v>
+        <v>-30.26032689450221</v>
       </c>
       <c r="HA7" t="n">
-        <v>-328.4466567607727</v>
+        <v>239.7218424962854</v>
       </c>
       <c r="HB7" t="n">
-        <v>-357.0701337295693</v>
+        <v>228.3292719167906</v>
       </c>
       <c r="HC7" t="n">
-        <v>-20.03245170876676</v>
+        <v>35.1221991084696</v>
       </c>
       <c r="HD7" t="n">
-        <v>-0.4528876645890019</v>
+        <v>-0.1155251432541327</v>
       </c>
       <c r="HE7" t="n">
-        <v>-0.287708908228968</v>
+        <v>-0.04676759020577859</v>
       </c>
       <c r="HF7" t="n">
-        <v>0.09495968748021608</v>
+        <v>-0.04902925962752336</v>
       </c>
       <c r="HG7" t="n">
-        <v>-0.3242192946908675</v>
+        <v>0.3028072152033988</v>
       </c>
       <c r="HH7" t="n">
-        <v>0.03097389753550279</v>
+        <v>-0.04271413341203056</v>
       </c>
       <c r="HI7" t="n">
-        <v>0.1187857190355514</v>
+        <v>-0.07940134458034998</v>
       </c>
       <c r="HJ7" t="n">
-        <v>-0.2003245170876673</v>
+        <v>0.3512219910846959</v>
       </c>
       <c r="HK7" t="n">
-        <v>-0.2223959077561622</v>
+        <v>0.2562352472002474</v>
       </c>
       <c r="HL7" t="n">
-        <v>-0.01313951291767464</v>
+        <v>0.02754313795975193</v>
       </c>
       <c r="HM7" t="n">
-        <v>-0.2116805421610592</v>
+        <v>0.1510514704747496</v>
       </c>
       <c r="HN7" t="n">
-        <v>-0.1853057238572048</v>
+        <v>0.1707804207037422</v>
       </c>
       <c r="HO7" t="n">
-        <v>0.03787976873762156</v>
+        <v>-0.04417583795889872</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -5588,25 +5588,25 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5627,49 +5627,49 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
@@ -5684,13 +5684,13 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
         <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -5711,13 +5711,13 @@
         <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -5726,16 +5726,16 @@
         <v>1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD8" t="n">
         <v>0</v>
@@ -5759,133 +5759,133 @@
         <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL8" t="n">
         <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.145616641901932</v>
+        <v>2.912332838038633</v>
       </c>
       <c r="BN8" t="n">
-        <v>7.724219910846954</v>
+        <v>5.825854383358099</v>
       </c>
       <c r="BO8" t="n">
-        <v>41.62496285289747</v>
+        <v>28.68112927191679</v>
       </c>
       <c r="BP8" t="n">
-        <v>16.73580980683506</v>
+        <v>10.7554234769688</v>
       </c>
       <c r="BQ8" t="n">
-        <v>133.0282317979197</v>
+        <v>120.1022288261516</v>
       </c>
       <c r="BR8" t="n">
-        <v>17.16493313521545</v>
+        <v>24.64784546805349</v>
       </c>
       <c r="BS8" t="n">
-        <v>10.72808320950966</v>
+        <v>13.444279346211</v>
       </c>
       <c r="BT8" t="n">
-        <v>31.3260029717682</v>
+        <v>45.71054977711739</v>
       </c>
       <c r="BU8" t="n">
-        <v>1680.017830609213</v>
+        <v>1364.594353640416</v>
       </c>
       <c r="BV8" t="n">
-        <v>29.18038632986627</v>
+        <v>34.50698365527489</v>
       </c>
       <c r="BW8" t="n">
-        <v>14.59019316493313</v>
+        <v>17.02942050520059</v>
       </c>
       <c r="BX8" t="n">
-        <v>18.02317979197623</v>
+        <v>31.81812778603269</v>
       </c>
       <c r="BY8" t="n">
-        <v>42.91233283803863</v>
+        <v>64.53254086181278</v>
       </c>
       <c r="BZ8" t="n">
-        <v>3.432986627043091</v>
+        <v>1.792570579494799</v>
       </c>
       <c r="CA8" t="n">
-        <v>10.72808320950966</v>
+        <v>18.82199108469539</v>
       </c>
       <c r="CB8" t="n">
-        <v>36.04635958395245</v>
+        <v>47.05497771173849</v>
       </c>
       <c r="CC8" t="n">
-        <v>129.1661218424963</v>
+        <v>155.0573551263002</v>
       </c>
       <c r="CD8" t="n">
-        <v>1435.846656760773</v>
+        <v>1098.397622585438</v>
       </c>
       <c r="CE8" t="n">
-        <v>1253.040118870728</v>
+        <v>889.5631500742942</v>
       </c>
       <c r="CF8" t="n">
-        <v>186.7544725111441</v>
+        <v>177.2404160475483</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.4226165711455458</v>
+        <v>0.4746063908025274</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.860747187433666</v>
+        <v>0.9089948519369023</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.2467459138187221</v>
+        <v>0.3855344812516389</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.7903021297672114</v>
+        <v>0.7493208635608776</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.04688860007933864</v>
+        <v>0.09524037242236823</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.1971401585016824</v>
+        <v>0.3527347527495435</v>
       </c>
       <c r="CM8" t="n">
-        <v>1.867544725111441</v>
+        <v>1.772404160475483</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.9081212389694848</v>
+        <v>1.010465174147039</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.1082353557188287</v>
+        <v>0.1201281620122414</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.333503229676771</v>
+        <v>1.20063823351066</v>
       </c>
       <c r="CQ8" t="n">
-        <v>1.278731330117417</v>
+        <v>1.190447301870369</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.06324793593052382</v>
+        <v>0.1256804593741946</v>
       </c>
       <c r="CS8" t="n">
         <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
         <v>1</v>
@@ -5906,13 +5906,13 @@
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK8" t="n">
         <v>1</v>
@@ -5927,37 +5927,37 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP8" t="n">
         <v>1</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS8" t="n">
         <v>1</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX8" t="n">
         <v>0</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DZ8" t="n">
         <v>1</v>
@@ -5966,7 +5966,7 @@
         <v>1</v>
       </c>
       <c r="EB8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC8" t="n">
         <v>0</v>
@@ -5975,22 +5975,22 @@
         <v>1</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EI8" t="n">
         <v>1</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK8" t="n">
         <v>1</v>
@@ -6005,16 +6005,16 @@
         <v>1</v>
       </c>
       <c r="EO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
         <v>1</v>
@@ -6023,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV8" t="n">
         <v>1</v>
@@ -6035,10 +6035,10 @@
         <v>1</v>
       </c>
       <c r="EY8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA8" t="n">
         <v>0</v>
@@ -6050,201 +6050,201 @@
         <v>1</v>
       </c>
       <c r="FD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FE8" t="n">
-        <v>1.300148588410104</v>
+        <v>1.864784546805349</v>
       </c>
       <c r="FF8" t="n">
-        <v>1.933135215453194</v>
+        <v>2.617533432392273</v>
       </c>
       <c r="FG8" t="n">
-        <v>20.8778603268945</v>
+        <v>23.99405646359584</v>
       </c>
       <c r="FH8" t="n">
-        <v>6.9592867756315</v>
+        <v>6.543833580980684</v>
       </c>
       <c r="FI8" t="n">
-        <v>96.27013372956908</v>
+        <v>82.888558692422</v>
       </c>
       <c r="FJ8" t="n">
-        <v>23.19762258543833</v>
+        <v>26.17533432392274</v>
       </c>
       <c r="FK8" t="n">
-        <v>11.21218424962853</v>
+        <v>9.161367013372958</v>
       </c>
       <c r="FL8" t="n">
-        <v>28.61040118870728</v>
+        <v>39.2630014858841</v>
       </c>
       <c r="FM8" t="n">
-        <v>1112.712630014859</v>
+        <v>1090.202674591382</v>
       </c>
       <c r="FN8" t="n">
-        <v>30.15690936106983</v>
+        <v>36.20921248142646</v>
       </c>
       <c r="FO8" t="n">
-        <v>15.07845468053492</v>
+        <v>18.75898959881129</v>
       </c>
       <c r="FP8" t="n">
-        <v>32.47667161961367</v>
+        <v>34.90044576523032</v>
       </c>
       <c r="FQ8" t="n">
-        <v>48.32838038632986</v>
+        <v>67.18335809806835</v>
       </c>
       <c r="FR8" t="n">
-        <v>5.799405646359583</v>
+        <v>3.490044576523032</v>
       </c>
       <c r="FS8" t="n">
-        <v>13.53194650817236</v>
+        <v>17.88647845468054</v>
       </c>
       <c r="FT8" t="n">
-        <v>38.27607726597325</v>
+        <v>41.444279346211</v>
       </c>
       <c r="FU8" t="n">
-        <v>146.9182763744428</v>
+        <v>160.5420505200594</v>
       </c>
       <c r="FV8" t="n">
-        <v>900.8410104011886</v>
+        <v>830.6306092124815</v>
       </c>
       <c r="FW8" t="n">
-        <v>712.5536404160475</v>
+        <v>605.0864784546806</v>
       </c>
       <c r="FX8" t="n">
-        <v>152.9109955423477</v>
+        <v>155.961367013373</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.1449851411589896</v>
+        <v>0.3271916790490342</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.6183731338003254</v>
+        <v>0.6543833580980684</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.2153252712674966</v>
+        <v>0.5755984246717023</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.6389093111241525</v>
+        <v>1.046506445771324</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.06130427761561662</v>
+        <v>0.1088710033922443</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.3163586049668112</v>
+        <v>0.4643375094605716</v>
       </c>
       <c r="GE8" t="n">
-        <v>1.529109955423477</v>
+        <v>1.55961367013373</v>
       </c>
       <c r="GF8" t="n">
-        <v>1.011266502134838</v>
+        <v>0.9782849197069433</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.1033935621457183</v>
+        <v>0.09291267122985247</v>
       </c>
       <c r="GH8" t="n">
-        <v>0.9655524439519402</v>
+        <v>0.8315641412377639</v>
       </c>
       <c r="GI8" t="n">
-        <v>0.970887556777586</v>
+        <v>0.8789819114255867</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.08571807867561373</v>
+        <v>0.1359299975984379</v>
       </c>
       <c r="GK8" t="n">
-        <v>5.79108469539376</v>
+        <v>3.208320950965825</v>
       </c>
       <c r="GL8" t="n">
-        <v>20.74710252600297</v>
+        <v>4.687072808320949</v>
       </c>
       <c r="GM8" t="n">
-        <v>9.776523031203563</v>
+        <v>4.211589895988111</v>
       </c>
       <c r="GN8" t="n">
-        <v>36.75809806835066</v>
+        <v>37.21367013372956</v>
       </c>
       <c r="GO8" t="n">
-        <v>-6.032689450222879</v>
+        <v>-1.527488855869244</v>
       </c>
       <c r="GP8" t="n">
-        <v>-0.4841010401188708</v>
+        <v>4.282912332838038</v>
       </c>
       <c r="GQ8" t="n">
-        <v>2.715601783060922</v>
+        <v>6.447548291233282</v>
       </c>
       <c r="GR8" t="n">
-        <v>567.3052005943537</v>
+        <v>274.3916790490341</v>
       </c>
       <c r="GS8" t="n">
-        <v>-0.9765230312035627</v>
+        <v>-1.702228826151568</v>
       </c>
       <c r="GT8" t="n">
-        <v>-0.4882615156017813</v>
+        <v>-1.729569093610699</v>
       </c>
       <c r="GU8" t="n">
-        <v>-14.45349182763744</v>
+        <v>-3.082317979197626</v>
       </c>
       <c r="GV8" t="n">
-        <v>-5.416047548291232</v>
+        <v>-2.650817236255577</v>
       </c>
       <c r="GW8" t="n">
-        <v>-2.366419019316492</v>
+        <v>-1.697473997028232</v>
       </c>
       <c r="GX8" t="n">
-        <v>-2.803863298662703</v>
+        <v>0.9355126300148591</v>
       </c>
       <c r="GY8" t="n">
-        <v>-2.229717682020798</v>
+        <v>5.61069836552749</v>
       </c>
       <c r="GZ8" t="n">
-        <v>-17.75215453194647</v>
+        <v>-5.484695393759267</v>
       </c>
       <c r="HA8" t="n">
-        <v>535.0056463595841</v>
+        <v>267.7670133729567</v>
       </c>
       <c r="HB8" t="n">
-        <v>540.4864784546805</v>
+        <v>284.4766716196136</v>
       </c>
       <c r="HC8" t="n">
-        <v>33.84347696879644</v>
+        <v>21.2790490341753</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.2776314299865563</v>
+        <v>0.1474147117534932</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.2423740536333405</v>
+        <v>0.254611493838834</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.03142064255122554</v>
+        <v>-0.1900639434200634</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.1513928186430589</v>
+        <v>-0.2971855822104467</v>
       </c>
       <c r="HH8" t="n">
-        <v>-0.01441567753627798</v>
+        <v>-0.0136306309698761</v>
       </c>
       <c r="HI8" t="n">
-        <v>-0.1192184464651288</v>
+        <v>-0.1116027567110281</v>
       </c>
       <c r="HJ8" t="n">
-        <v>0.3384347696879644</v>
+        <v>0.2127904903417532</v>
       </c>
       <c r="HK8" t="n">
-        <v>-0.1031452631653533</v>
+        <v>0.03218025444009542</v>
       </c>
       <c r="HL8" t="n">
-        <v>0.004841793573110348</v>
+        <v>0.02721549078238897</v>
       </c>
       <c r="HM8" t="n">
-        <v>0.3679507857248304</v>
+        <v>0.3690740922728959</v>
       </c>
       <c r="HN8" t="n">
-        <v>0.3078437733398306</v>
+        <v>0.3114653904447821</v>
       </c>
       <c r="HO8" t="n">
-        <v>-0.02247014274508992</v>
+        <v>-0.01024953822424335</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -6253,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -6262,10 +6262,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -6277,19 +6277,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -6301,22 +6301,22 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -6325,10 +6325,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
@@ -6340,7 +6340,7 @@
         <v>1</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -6361,22 +6361,22 @@
         <v>1</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
@@ -6394,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ9" t="n">
         <v>1</v>
@@ -6403,10 +6403,10 @@
         <v>1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
         <v>0</v>
@@ -6415,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG9" t="n">
         <v>1</v>
@@ -6424,154 +6424,154 @@
         <v>1</v>
       </c>
       <c r="BI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
         <v>1</v>
       </c>
       <c r="BK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.664190193164933</v>
+        <v>3.417533432392273</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.143239227340267</v>
+        <v>5.58662704309064</v>
       </c>
       <c r="BO9" t="n">
-        <v>21.55364041604755</v>
+        <v>29.45676077265973</v>
       </c>
       <c r="BP9" t="n">
-        <v>7.633580980683506</v>
+        <v>12.1890044576523</v>
       </c>
       <c r="BQ9" t="n">
-        <v>98.33848439821693</v>
+        <v>136.6184249628529</v>
       </c>
       <c r="BR9" t="n">
-        <v>28.73818722139673</v>
+        <v>24.88588410104012</v>
       </c>
       <c r="BS9" t="n">
-        <v>9.878751857355127</v>
+        <v>16.25200594353641</v>
       </c>
       <c r="BT9" t="n">
-        <v>37.26983655274889</v>
+        <v>46.21664190193165</v>
       </c>
       <c r="BU9" t="n">
-        <v>1224.067161961367</v>
+        <v>1627.739970282318</v>
       </c>
       <c r="BV9" t="n">
-        <v>35.47369985141159</v>
+        <v>34.53551263001486</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.57295690936107</v>
+        <v>15.74413075780089</v>
       </c>
       <c r="BX9" t="n">
-        <v>19.30846953937593</v>
+        <v>41.13789004457653</v>
       </c>
       <c r="BY9" t="n">
-        <v>57.47637444279346</v>
+        <v>58.91352154531947</v>
       </c>
       <c r="BZ9" t="n">
-        <v>4.939375928677563</v>
+        <v>5.078751857355127</v>
       </c>
       <c r="CA9" t="n">
-        <v>17.51233283803863</v>
+        <v>24.37800891530461</v>
       </c>
       <c r="CB9" t="n">
-        <v>39.96404160475483</v>
+        <v>44.1851411589896</v>
       </c>
       <c r="CC9" t="n">
-        <v>152.6716196136701</v>
+        <v>153.3783060921248</v>
       </c>
       <c r="CD9" t="n">
-        <v>999.550074294205</v>
+        <v>1350.440118870728</v>
       </c>
       <c r="CE9" t="n">
-        <v>775.0329866270431</v>
+        <v>1114.78603268945</v>
       </c>
       <c r="CF9" t="n">
-        <v>170.5880832095096</v>
+        <v>207.2638632986627</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.367151472773359</v>
+        <v>0.5542226337629758</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.7721626897415728</v>
+        <v>1.014889312258883</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.3837624798843224</v>
+        <v>0.5583366240564959</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.193723636442804</v>
+        <v>0.9325583681804843</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.080810999130064</v>
+        <v>0.07938961062151298</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.3804988906661612</v>
+        <v>0.310119403913664</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.705880832095097</v>
+        <v>2.072638632986627</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.7124908124616071</v>
+        <v>1.504197315974434</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.08827075640354008</v>
+        <v>0.1112295224857242</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.9866899386279759</v>
+        <v>1.3624877993499</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.9992493927091187</v>
+        <v>1.35266348198875</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.1022947833756688</v>
+        <v>0.1088320733546617</v>
       </c>
       <c r="CS9" t="n">
         <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
@@ -6580,10 +6580,10 @@
         <v>1</v>
       </c>
       <c r="DI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK9" t="n">
         <v>1</v>
@@ -6592,28 +6592,28 @@
         <v>1</v>
       </c>
       <c r="DM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR9" t="n">
         <v>0</v>
       </c>
       <c r="DS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU9" t="n">
         <v>1</v>
@@ -6625,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -6634,31 +6634,31 @@
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH9" t="n">
         <v>1</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ9" t="n">
         <v>1</v>
@@ -6670,19 +6670,19 @@
         <v>1</v>
       </c>
       <c r="EM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
@@ -6691,16 +6691,16 @@
         <v>0</v>
       </c>
       <c r="ET9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EU9" t="n">
         <v>1</v>
       </c>
       <c r="EV9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>0</v>
@@ -6712,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FB9" t="n">
         <v>0</v>
@@ -6724,193 +6724,193 @@
         <v>1</v>
       </c>
       <c r="FE9" t="n">
-        <v>1.939078751857355</v>
+        <v>1.87964338781575</v>
       </c>
       <c r="FF9" t="n">
-        <v>3.27221396731055</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>35.99435364041605</v>
+        <v>41.01901931649331</v>
       </c>
       <c r="FH9" t="n">
-        <v>10.28410104011887</v>
+        <v>10.37830609212481</v>
       </c>
       <c r="FI9" t="n">
-        <v>114.9949479940565</v>
+        <v>129.4817236255572</v>
       </c>
       <c r="FJ9" t="n">
-        <v>22.90549777117385</v>
+        <v>24.21604754829123</v>
       </c>
       <c r="FK9" t="n">
-        <v>14.02377414561664</v>
+        <v>20.75661218424963</v>
       </c>
       <c r="FL9" t="n">
-        <v>48.61575037147103</v>
+        <v>63.25824665676077</v>
       </c>
       <c r="FM9" t="n">
-        <v>1416.401188707281</v>
+        <v>1610.120059435364</v>
       </c>
       <c r="FN9" t="n">
-        <v>31.78722139673106</v>
+        <v>41.51322436849925</v>
       </c>
       <c r="FO9" t="n">
-        <v>20.56820208023774</v>
+        <v>25.20445765230312</v>
       </c>
       <c r="FP9" t="n">
-        <v>34.12451708766717</v>
+        <v>31.62912332838038</v>
       </c>
       <c r="FQ9" t="n">
-        <v>68.71649331352154</v>
+        <v>59.30460624071321</v>
       </c>
       <c r="FR9" t="n">
-        <v>6.076968796433879</v>
+        <v>5.436255572065378</v>
       </c>
       <c r="FS9" t="n">
-        <v>18.23090638930163</v>
+        <v>23.22763744427935</v>
       </c>
       <c r="FT9" t="n">
-        <v>61.70460624071323</v>
+        <v>43.98424962852897</v>
       </c>
       <c r="FU9" t="n">
-        <v>154.2615156017831</v>
+        <v>138.3774145616642</v>
       </c>
       <c r="FV9" t="n">
-        <v>1119.564635958395</v>
+        <v>1333.859435364041</v>
       </c>
       <c r="FW9" t="n">
-        <v>889.1072808320951</v>
+        <v>1096.641010401189</v>
       </c>
       <c r="FX9" t="n">
-        <v>181.701367013373</v>
+        <v>202.7723328380386</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.2355780569137885</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.5787328979539819</v>
+        <v>0.643977488625856</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.5864731601509795</v>
+        <v>0.2879813409793306</v>
       </c>
       <c r="GB9" t="n">
-        <v>1.0187385356356</v>
+        <v>0.8899981868494234</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.09947482869185544</v>
+        <v>0.1167196807392411</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.346341952677462</v>
+        <v>0.2646980783008478</v>
       </c>
       <c r="GE9" t="n">
-        <v>1.81701367013373</v>
+        <v>2.027723328380386</v>
       </c>
       <c r="GF9" t="n">
-        <v>1.139121291944723</v>
+        <v>1.384384964333281</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.1170345956646778</v>
+        <v>0.1365906254900087</v>
       </c>
       <c r="GH9" t="n">
-        <v>1.150478104465678</v>
+        <v>1.289391315338394</v>
       </c>
       <c r="GI9" t="n">
-        <v>1.151041512505245</v>
+        <v>1.271924914437862</v>
       </c>
       <c r="GJ9" t="n">
-        <v>0.1284764099907557</v>
+        <v>0.1562235087085114</v>
       </c>
       <c r="GK9" t="n">
-        <v>-0.1289747399702823</v>
+        <v>5.58662704309064</v>
       </c>
       <c r="GL9" t="n">
-        <v>-14.4407132243685</v>
+        <v>-11.56225854383358</v>
       </c>
       <c r="GM9" t="n">
-        <v>-2.650520059435365</v>
+        <v>1.810698365527491</v>
       </c>
       <c r="GN9" t="n">
-        <v>-16.65646359583954</v>
+        <v>7.136701337295733</v>
       </c>
       <c r="GO9" t="n">
-        <v>5.83268945022288</v>
+        <v>0.6698365527488903</v>
       </c>
       <c r="GP9" t="n">
-        <v>-4.145022288261515</v>
+        <v>-4.504606240713219</v>
       </c>
       <c r="GQ9" t="n">
-        <v>-11.34591381872214</v>
+        <v>-17.04160475482912</v>
       </c>
       <c r="GR9" t="n">
-        <v>-192.3340267459137</v>
+        <v>17.61991084695433</v>
       </c>
       <c r="GS9" t="n">
-        <v>3.686478454680532</v>
+        <v>-6.977711738484388</v>
       </c>
       <c r="GT9" t="n">
-        <v>-7.995245170876673</v>
+        <v>-9.460326894502222</v>
       </c>
       <c r="GU9" t="n">
-        <v>-14.81604754829124</v>
+        <v>9.508766716196146</v>
       </c>
       <c r="GV9" t="n">
-        <v>-11.24011887072808</v>
+        <v>-0.3910846953937437</v>
       </c>
       <c r="GW9" t="n">
-        <v>-1.137592867756315</v>
+        <v>-0.3575037147102513</v>
       </c>
       <c r="GX9" t="n">
-        <v>-0.7185735512630025</v>
+        <v>1.150371471025263</v>
       </c>
       <c r="GY9" t="n">
-        <v>-21.74056463595839</v>
+        <v>0.2008915304606305</v>
       </c>
       <c r="GZ9" t="n">
-        <v>-1.589895988112914</v>
+        <v>15.00089153046065</v>
       </c>
       <c r="HA9" t="n">
-        <v>-120.0145616641902</v>
+        <v>16.58068350668691</v>
       </c>
       <c r="HB9" t="n">
-        <v>-114.074294205052</v>
+        <v>18.14502228826177</v>
       </c>
       <c r="HC9" t="n">
-        <v>-11.11328380386334</v>
+        <v>4.491530460624119</v>
       </c>
       <c r="HD9" t="n">
-        <v>0.1315734158595704</v>
+        <v>0.5542226337629758</v>
       </c>
       <c r="HE9" t="n">
-        <v>0.1934297917875909</v>
+        <v>0.3709118236330273</v>
       </c>
       <c r="HF9" t="n">
-        <v>-0.2027106802666571</v>
+        <v>0.2703552830771652</v>
       </c>
       <c r="HG9" t="n">
-        <v>0.1749851008072045</v>
+        <v>0.04256018133106088</v>
       </c>
       <c r="HH9" t="n">
-        <v>-0.01866382956179144</v>
+        <v>-0.03733007011772815</v>
       </c>
       <c r="HI9" t="n">
-        <v>0.03415693798869918</v>
+        <v>0.04542132561281614</v>
       </c>
       <c r="HJ9" t="n">
-        <v>-0.1111328380386332</v>
+        <v>0.04491530460624116</v>
       </c>
       <c r="HK9" t="n">
-        <v>-0.4266304794831156</v>
+        <v>0.1198123516411527</v>
       </c>
       <c r="HL9" t="n">
-        <v>-0.02876383926113772</v>
+        <v>-0.02536110300428455</v>
       </c>
       <c r="HM9" t="n">
-        <v>-0.1637881658377016</v>
+        <v>0.0730964840115067</v>
       </c>
       <c r="HN9" t="n">
-        <v>-0.1517921197961264</v>
+        <v>0.08073856755088737</v>
       </c>
       <c r="HO9" t="n">
-        <v>-0.02618162661508688</v>
+        <v>-0.04739143535384971</v>
       </c>
     </row>
     <row r="10">
@@ -6921,31 +6921,31 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -6957,10 +6957,10 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -6969,16 +6969,16 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -6987,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -6999,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -7017,10 +7017,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
         <v>1</v>
@@ -7029,16 +7029,16 @@
         <v>1</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
         <v>1</v>
@@ -7047,43 +7047,43 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT10" t="n">
         <v>1</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
         <v>1</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>1</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI10" t="n">
         <v>1</v>
@@ -7104,112 +7104,112 @@
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.87964338781575</v>
+        <v>3.328380386329866</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.906686478454681</v>
+        <v>5.558692421991084</v>
       </c>
       <c r="BO10" t="n">
-        <v>36.22704309063893</v>
+        <v>22.97592867756315</v>
       </c>
       <c r="BP10" t="n">
-        <v>12.39346210995542</v>
+        <v>11.11738484398217</v>
       </c>
       <c r="BQ10" t="n">
-        <v>119.6445765230312</v>
+        <v>111.1738484398217</v>
       </c>
       <c r="BR10" t="n">
-        <v>20.49687964338781</v>
+        <v>20.38187221396731</v>
       </c>
       <c r="BS10" t="n">
-        <v>17.6368499257058</v>
+        <v>6.299851411589895</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.15393759286775</v>
+        <v>27.05230312035661</v>
       </c>
       <c r="BU10" t="n">
-        <v>1498.178900445765</v>
+        <v>1426.731054977712</v>
       </c>
       <c r="BV10" t="n">
-        <v>35.75037147102526</v>
+        <v>21.86419019316493</v>
       </c>
       <c r="BW10" t="n">
-        <v>26.69361069836553</v>
+        <v>13.3408618127786</v>
       </c>
       <c r="BX10" t="n">
-        <v>35.75037147102526</v>
+        <v>20.0112927191679</v>
       </c>
       <c r="BY10" t="n">
-        <v>69.11738484398217</v>
+        <v>57.06924219910847</v>
       </c>
       <c r="BZ10" t="n">
-        <v>6.196731054977712</v>
+        <v>2.964635958395245</v>
       </c>
       <c r="CA10" t="n">
-        <v>24.78692421991085</v>
+        <v>10.00564635958395</v>
       </c>
       <c r="CB10" t="n">
-        <v>42.90044576523031</v>
+        <v>35.20505200594354</v>
       </c>
       <c r="CC10" t="n">
-        <v>143.001485884101</v>
+        <v>93.38603268945022</v>
       </c>
       <c r="CD10" t="n">
-        <v>1224.569390787518</v>
+        <v>1206.236255572065</v>
       </c>
       <c r="CE10" t="n">
-        <v>993.8603268945022</v>
+        <v>1053.928083209509</v>
       </c>
       <c r="CF10" t="n">
-        <v>192.4323328380386</v>
+        <v>160.1273997028232</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.1588905398712234</v>
+        <v>0.5299497528760704</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.8490129067971914</v>
+        <v>1.002980433021513</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.1777632849916741</v>
+        <v>0.1501822163134433</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.7450882741941216</v>
+        <v>0.75708740648054</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.1132199488585414</v>
+        <v>0.03843020697962001</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.291509603014089</v>
+        <v>0.1589714060501695</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.924323328380386</v>
+        <v>1.601273997028232</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.308787926331695</v>
+        <v>0.970859454232411</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.1240173062218804</v>
+        <v>0.08962630413085504</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.192478711946737</v>
+        <v>1.112983876589738</v>
       </c>
       <c r="CQ10" t="n">
-        <v>1.192182810325538</v>
+        <v>1.093402409726526</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1480753972745459</v>
+        <v>0.04708526465935672</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT10" t="n">
         <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV10" t="n">
         <v>1</v>
@@ -7221,31 +7221,31 @@
         <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA10" t="n">
         <v>1</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
         <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH10" t="n">
         <v>0</v>
@@ -7269,16 +7269,16 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>1</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV10" t="n">
         <v>1</v>
       </c>
       <c r="DW10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -7305,52 +7305,52 @@
         <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
         <v>1</v>
       </c>
       <c r="EG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ10" t="n">
         <v>1</v>
       </c>
       <c r="EK10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
         <v>1</v>
       </c>
       <c r="EM10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EQ10" t="n">
         <v>1</v>
@@ -7359,10 +7359,10 @@
         <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ET10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>1</v>
@@ -7377,13 +7377,13 @@
         <v>1</v>
       </c>
       <c r="EY10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
         <v>1</v>
@@ -7395,193 +7395,193 @@
         <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>2.236255572065379</v>
+        <v>2.117384843982169</v>
       </c>
       <c r="FF10" t="n">
-        <v>4.814264487369985</v>
+        <v>3.580980683506687</v>
       </c>
       <c r="FG10" t="n">
-        <v>32.2555720653789</v>
+        <v>25.06686478454681</v>
       </c>
       <c r="FH10" t="n">
-        <v>12.03566121842496</v>
+        <v>8.594353640416047</v>
       </c>
       <c r="FI10" t="n">
-        <v>122.7637444279346</v>
+        <v>86.30163447251115</v>
       </c>
       <c r="FJ10" t="n">
-        <v>21.66419019316493</v>
+        <v>20.41158989598812</v>
       </c>
       <c r="FK10" t="n">
-        <v>11.55423476968796</v>
+        <v>10.74294205052006</v>
       </c>
       <c r="FL10" t="n">
-        <v>42.84695393759286</v>
+        <v>31.15453194650817</v>
       </c>
       <c r="FM10" t="n">
-        <v>1541.046062407132</v>
+        <v>1009.120356612184</v>
       </c>
       <c r="FN10" t="n">
-        <v>38.99554234769688</v>
+        <v>23.63447251114413</v>
       </c>
       <c r="FO10" t="n">
-        <v>18.29420505200594</v>
+        <v>16.47251114413076</v>
       </c>
       <c r="FP10" t="n">
-        <v>29.84843982169391</v>
+        <v>28.64784546805349</v>
       </c>
       <c r="FQ10" t="n">
-        <v>62.5854383358098</v>
+        <v>64.45765230312035</v>
       </c>
       <c r="FR10" t="n">
-        <v>3.369985141158989</v>
+        <v>0.3580980683506687</v>
       </c>
       <c r="FS10" t="n">
-        <v>21.18276374442793</v>
+        <v>15.04011887072808</v>
       </c>
       <c r="FT10" t="n">
-        <v>44.77265973254087</v>
+        <v>32.58692421991085</v>
       </c>
       <c r="FU10" t="n">
-        <v>155.9821693907875</v>
+        <v>128.9153046062407</v>
       </c>
       <c r="FV10" t="n">
-        <v>1283.964338781575</v>
+        <v>797.1263001485884</v>
       </c>
       <c r="FW10" t="n">
-        <v>1049.02823179792</v>
+        <v>625.2392273402675</v>
       </c>
       <c r="FX10" t="n">
-        <v>196.7589895988113</v>
+        <v>139.765676077266</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.4139818576668502</v>
+        <v>0.258246429734936</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.9531939086173856</v>
+        <v>0.6077271648900003</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.3438760348121417</v>
+        <v>0.1924024810518561</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.8119295266397792</v>
+        <v>0.566298993594466</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.07792153329260855</v>
+        <v>0.06954491513042473</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.2902677416536255</v>
+        <v>0.2961226804388565</v>
       </c>
       <c r="GE10" t="n">
-        <v>1.967589895988113</v>
+        <v>1.39765676077266</v>
       </c>
       <c r="GF10" t="n">
-        <v>1.226873275313097</v>
+        <v>0.9049266418625183</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.1134925277392343</v>
+        <v>0.08383052682526704</v>
       </c>
       <c r="GH10" t="n">
-        <v>1.225687650185138</v>
+        <v>0.8633643144748596</v>
       </c>
       <c r="GI10" t="n">
-        <v>1.209208215972603</v>
+        <v>0.8788247623751241</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.09873935644704829</v>
+        <v>0.09381988302844642</v>
       </c>
       <c r="GK10" t="n">
-        <v>-2.907578008915304</v>
+        <v>1.977711738484398</v>
       </c>
       <c r="GL10" t="n">
-        <v>3.97147102526003</v>
+        <v>-2.090936106983655</v>
       </c>
       <c r="GM10" t="n">
-        <v>0.3578008915304611</v>
+        <v>2.523031203566122</v>
       </c>
       <c r="GN10" t="n">
-        <v>-3.119167904903406</v>
+        <v>24.87221396731053</v>
       </c>
       <c r="GO10" t="n">
-        <v>-1.167310549777117</v>
+        <v>-0.02971768202080582</v>
       </c>
       <c r="GP10" t="n">
-        <v>6.082615156017832</v>
+        <v>-4.443090638930165</v>
       </c>
       <c r="GQ10" t="n">
-        <v>15.30698365527488</v>
+        <v>-4.102228826151563</v>
       </c>
       <c r="GR10" t="n">
-        <v>-42.86716196136695</v>
+        <v>417.6106983655274</v>
       </c>
       <c r="GS10" t="n">
-        <v>-3.245170876671615</v>
+        <v>-1.770282317979198</v>
       </c>
       <c r="GT10" t="n">
-        <v>8.399405646359583</v>
+        <v>-3.131649331352154</v>
       </c>
       <c r="GU10" t="n">
-        <v>5.901931649331353</v>
+        <v>-8.636552748885588</v>
       </c>
       <c r="GV10" t="n">
-        <v>6.531946508172361</v>
+        <v>-7.388410104011889</v>
       </c>
       <c r="GW10" t="n">
-        <v>2.826745913818723</v>
+        <v>2.606537890044577</v>
       </c>
       <c r="GX10" t="n">
-        <v>3.604160475482914</v>
+        <v>-5.034472511144132</v>
       </c>
       <c r="GY10" t="n">
-        <v>-1.872213967310557</v>
+        <v>2.618127786032687</v>
       </c>
       <c r="GZ10" t="n">
-        <v>-12.98068350668646</v>
+        <v>-35.52927191679049</v>
       </c>
       <c r="HA10" t="n">
-        <v>-59.39494799405657</v>
+        <v>409.109955423477</v>
       </c>
       <c r="HB10" t="n">
-        <v>-55.16790490341748</v>
+        <v>428.6888558692419</v>
       </c>
       <c r="HC10" t="n">
-        <v>-4.326656760772693</v>
+        <v>20.3617236255572</v>
       </c>
       <c r="HD10" t="n">
-        <v>-0.2550913177956268</v>
+        <v>0.2717033231411344</v>
       </c>
       <c r="HE10" t="n">
-        <v>-0.1041810018201942</v>
+        <v>0.3952532681315127</v>
       </c>
       <c r="HF10" t="n">
-        <v>-0.1661127498204676</v>
+        <v>-0.04222026473841278</v>
       </c>
       <c r="HG10" t="n">
-        <v>-0.06684125244565764</v>
+        <v>0.190788412886074</v>
       </c>
       <c r="HH10" t="n">
-        <v>0.03529841556593288</v>
+        <v>-0.03111470815080471</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.001241861360463559</v>
+        <v>-0.137151274388687</v>
       </c>
       <c r="HJ10" t="n">
-        <v>-0.04326656760772685</v>
+        <v>0.2036172362555717</v>
       </c>
       <c r="HK10" t="n">
-        <v>0.08191465101859841</v>
+        <v>0.06593281236989279</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.01052477848264603</v>
+        <v>0.005795777305588001</v>
       </c>
       <c r="HM10" t="n">
-        <v>-0.03320893823840088</v>
+        <v>0.2496195621148779</v>
       </c>
       <c r="HN10" t="n">
-        <v>-0.01702540564706556</v>
+        <v>0.2145776473514019</v>
       </c>
       <c r="HO10" t="n">
-        <v>0.04933604082749757</v>
+        <v>-0.0467346183690897</v>
       </c>
     </row>
   </sheetData>
